--- a/amc_book/Aditya Birla Sun Life Mutual Fund/Aditya Birla SL Flexi Cap Fund _G_/FACT_SHEET_2026-06-25.xlsx
+++ b/amc_book/Aditya Birla Sun Life Mutual Fund/Aditya Birla SL Flexi Cap Fund _G_/FACT_SHEET_2026-06-25.xlsx
@@ -618,34 +618,34 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3396605</v>
+        <v>3691683</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1131.3</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>384.2579</v>
+        <v>417.6401</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>1131.3</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>384.2579</v>
+        <v>417.6401</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>1098.1</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>372.9812</v>
+        <v>405.3837</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>3.0234</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>0.04486</v>
+        <v>0.04875</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1.4836</v>
+        <v>1.6125</v>
       </c>
     </row>
     <row r="7">
@@ -663,14 +663,14 @@
       <c r="H7" s="11" t="n"/>
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="13" t="n">
-        <v>384.258</v>
+        <v>417.64</v>
       </c>
       <c r="K7" s="11" t="n"/>
       <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="14" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="8">
@@ -698,34 +698,34 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>2426735</v>
+        <v>2637556</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>2145.3</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>520.6075</v>
+        <v>565.8348999999999</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>2145.3</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>520.6075</v>
+        <v>565.8348999999999</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>2122.8</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>515.1473</v>
+        <v>559.9004</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>1.0599</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>0.02131</v>
+        <v>0.02316</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>2.0101</v>
+        <v>2.1847</v>
       </c>
     </row>
     <row r="9">
@@ -753,34 +753,34 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1113503</v>
+        <v>1210238</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>2616</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>291.2924</v>
+        <v>316.5983</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>2616</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>291.2924</v>
+        <v>316.5983</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>2660</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>296.1918</v>
+        <v>321.9233</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>-1.6541</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>-0.0186</v>
+        <v>-0.02022</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>1.1247</v>
+        <v>1.2224</v>
       </c>
     </row>
     <row r="10">
@@ -808,34 +808,34 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>892925</v>
+        <v>970497</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>3054</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>272.6993</v>
+        <v>296.3898</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>3054</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>272.6993</v>
+        <v>296.3898</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>3170.5</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>283.1019</v>
+        <v>307.6961</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>-3.6745</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>-0.03869</v>
+        <v>-0.04205</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>1.0529</v>
+        <v>1.1444</v>
       </c>
     </row>
     <row r="11">
@@ -863,25 +863,25 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>3002524</v>
+        <v>3263366</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>619.25</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>185.9313</v>
+        <v>202.0839</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>619.25</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>185.9313</v>
+        <v>202.0839</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>619.2999</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>185.9463</v>
+        <v>202.1002</v>
       </c>
       <c r="M11" s="9" t="n">
         <v>-0.0081</v>
@@ -890,7 +890,7 @@
         <v>-6e-05</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>0.7179</v>
+        <v>0.7802</v>
       </c>
     </row>
     <row r="12">
@@ -908,14 +908,14 @@
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="13" t="n">
-        <v>1270.53</v>
+        <v>1380.907</v>
       </c>
       <c r="K12" s="11" t="n"/>
       <c r="L12" s="11" t="n"/>
       <c r="M12" s="11" t="n"/>
       <c r="N12" s="11" t="n"/>
       <c r="O12" s="14" t="n">
-        <v>4.91</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="13">
@@ -943,34 +943,34 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>522615</v>
+        <v>568017</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>9843</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>514.4099</v>
+        <v>559.0991</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>9843</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>514.4099</v>
+        <v>559.0991</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>9750</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>509.5496</v>
+        <v>553.8166</v>
       </c>
       <c r="M13" s="9" t="n">
         <v>0.9538</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>0.01894</v>
+        <v>0.02059</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>1.9861</v>
+        <v>2.1587</v>
       </c>
     </row>
     <row r="14">
@@ -998,34 +998,34 @@
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1090666</v>
+        <v>1185417</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>3182.2</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>347.0717</v>
+        <v>377.2234</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>3182.2</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>347.0717</v>
+        <v>377.2234</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>3064.5</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>334.2346</v>
+        <v>363.271</v>
       </c>
       <c r="M14" s="9" t="n">
         <v>3.8408</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>0.05147</v>
+        <v>0.05594</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>1.3401</v>
+        <v>1.4565</v>
       </c>
     </row>
     <row r="15">
@@ -1053,34 +1053,34 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>3413006</v>
+        <v>3709509</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>998.75</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>340.874</v>
+        <v>370.4872</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>998.75</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>340.874</v>
+        <v>370.4872</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>990.1</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>337.9217</v>
+        <v>367.2785</v>
       </c>
       <c r="M15" s="9" t="n">
         <v>0.8736</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0125</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>1.3161</v>
+        <v>1.4305</v>
       </c>
     </row>
     <row r="16">
@@ -1108,34 +1108,34 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>180363</v>
+        <v>196031</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>13745</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>247.9089</v>
+        <v>269.4446</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>13745</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>247.9089</v>
+        <v>269.4446</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>13248</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>238.9449</v>
+        <v>259.7019</v>
       </c>
       <c r="M16" s="9" t="n">
         <v>3.7515</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>0.03591</v>
+        <v>0.03903</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>0.9572000000000001</v>
+        <v>1.0403</v>
       </c>
     </row>
     <row r="17">
@@ -1153,14 +1153,14 @@
       <c r="H17" s="11" t="n"/>
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="13" t="n">
-        <v>1450.264</v>
+        <v>1576.254</v>
       </c>
       <c r="K17" s="11" t="n"/>
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="11" t="n"/>
       <c r="O17" s="14" t="n">
-        <v>5.6</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="18">
@@ -1188,34 +1188,34 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>4675933</v>
+        <v>5082151</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>1033.85</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>483.4213</v>
+        <v>525.4182</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>1033.85</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>483.4213</v>
+        <v>525.4182</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>1067.2</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>499.0156</v>
+        <v>542.3672</v>
       </c>
       <c r="M18" s="9" t="n">
         <v>-3.125</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>-0.05833</v>
+        <v>-0.06339</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>1.8665</v>
+        <v>2.0286</v>
       </c>
     </row>
     <row r="19">
@@ -1243,34 +1243,34 @@
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2790139</v>
+        <v>3032531</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1377.2</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>384.2579</v>
+        <v>417.6402</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>1377.2</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>384.2579</v>
+        <v>417.6402</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>1384.5</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>386.2947</v>
+        <v>419.8539</v>
       </c>
       <c r="M19" s="9" t="n">
         <v>-0.5273</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>-0.007820000000000001</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>1.4836</v>
+        <v>1.6125</v>
       </c>
     </row>
     <row r="20">
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>2724759</v>
+        <v>2961470</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1387.5</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>378.0603</v>
+        <v>410.904</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>1387.5</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>378.0603</v>
+        <v>410.904</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>1373.6</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>374.2729</v>
+        <v>406.7875</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>1.0119</v>
       </c>
       <c r="N20" s="10" t="n">
-        <v>0.01477</v>
+        <v>0.01605</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>1.4597</v>
+        <v>1.5865</v>
       </c>
     </row>
     <row r="21">
@@ -1353,34 +1353,34 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>8788927</v>
+        <v>9552459</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>409</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>359.4671</v>
+        <v>390.6956</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>409</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>359.4671</v>
+        <v>390.6956</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>405.95</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>356.7865</v>
+        <v>387.7821</v>
       </c>
       <c r="M21" s="9" t="n">
         <v>0.7513</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>0.01043</v>
+        <v>0.01133</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>1.3879</v>
+        <v>1.5085</v>
       </c>
     </row>
     <row r="22">
@@ -1408,34 +1408,34 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>8989117</v>
+        <v>9770040</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>324.05</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>291.2923</v>
+        <v>316.5981</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>324.05</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>291.2923</v>
+        <v>316.5981</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>325.2</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>292.3261</v>
+        <v>317.7217</v>
       </c>
       <c r="M22" s="9" t="n">
         <v>-0.3536</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>-0.00398</v>
+        <v>-0.00432</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>1.1247</v>
+        <v>1.2224</v>
       </c>
     </row>
     <row r="23">
@@ -1463,34 +1463,34 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>3580241</v>
+        <v>3891272</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>796.3</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>285.0946</v>
+        <v>309.862</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>796.3</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>285.0946</v>
+        <v>309.862</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>793.2</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>283.9847</v>
+        <v>308.6557</v>
       </c>
       <c r="M23" s="9" t="n">
         <v>0.3908</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.00468</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>1.1008</v>
+        <v>1.1964</v>
       </c>
     </row>
     <row r="24">
@@ -1518,34 +1518,34 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>2549278</v>
+        <v>2770744</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1045.4</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>266.5015</v>
+        <v>289.6536</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>1045.4</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>266.5015</v>
+        <v>289.6536</v>
       </c>
       <c r="K24" s="7" t="n">
         <v>1034.6</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>263.7483</v>
+        <v>286.6612</v>
       </c>
       <c r="M24" s="9" t="n">
         <v>1.0439</v>
       </c>
       <c r="N24" s="10" t="n">
-        <v>0.01074</v>
+        <v>0.01167</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>1.029</v>
+        <v>1.1184</v>
       </c>
     </row>
     <row r="25">
@@ -1563,14 +1563,14 @@
       <c r="H25" s="11" t="n"/>
       <c r="I25" s="11" t="n"/>
       <c r="J25" s="13" t="n">
-        <v>2448.095</v>
+        <v>2660.772</v>
       </c>
       <c r="K25" s="11" t="n"/>
       <c r="L25" s="11" t="n"/>
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
       <c r="O25" s="14" t="n">
-        <v>9.449999999999999</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="26">
@@ -1598,34 +1598,34 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1229897</v>
+        <v>1336743</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>3829.8</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>471.026</v>
+        <v>511.9458</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>3829.8</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>471.026</v>
+        <v>511.9458</v>
       </c>
       <c r="K26" s="7" t="n">
         <v>3757.7</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>462.1584</v>
+        <v>502.3079</v>
       </c>
       <c r="M26" s="9" t="n">
         <v>1.9187</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>0.03489</v>
+        <v>0.03793</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>1.8186</v>
+        <v>1.9766</v>
       </c>
     </row>
     <row r="27">
@@ -1653,34 +1653,34 @@
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1163553</v>
+        <v>1264636</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1384.9</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>161.1405</v>
+        <v>175.1394</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>1384.9</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>161.1405</v>
+        <v>175.1394</v>
       </c>
       <c r="K27" s="7" t="n">
         <v>1359.1</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>158.1385</v>
+        <v>171.8767</v>
       </c>
       <c r="M27" s="9" t="n">
         <v>1.8983</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>0.01181</v>
+        <v>0.01284</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>0.6222</v>
+        <v>0.6762</v>
       </c>
     </row>
     <row r="28">
@@ -1698,14 +1698,14 @@
       <c r="H28" s="11" t="n"/>
       <c r="I28" s="11" t="n"/>
       <c r="J28" s="13" t="n">
-        <v>632.167</v>
+        <v>687.085</v>
       </c>
       <c r="K28" s="11" t="n"/>
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="11" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="14" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="29">
@@ -1733,34 +1733,34 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>13495384</v>
+        <v>14667786</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>335.25</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>452.4327</v>
+        <v>491.7375</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>335.25</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>452.4327</v>
+        <v>491.7375</v>
       </c>
       <c r="K29" s="7" t="n">
         <v>340.65</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>459.7203</v>
+        <v>499.6581</v>
       </c>
       <c r="M29" s="9" t="n">
         <v>-1.5852</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>-0.02769</v>
+        <v>-0.0301</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>1.7469</v>
+        <v>1.8986</v>
       </c>
     </row>
     <row r="30">
@@ -1778,14 +1778,14 @@
       <c r="H30" s="11" t="n"/>
       <c r="I30" s="11" t="n"/>
       <c r="J30" s="13" t="n">
-        <v>452.433</v>
+        <v>491.738</v>
       </c>
       <c r="K30" s="11" t="n"/>
       <c r="L30" s="11" t="n"/>
       <c r="M30" s="11" t="n"/>
       <c r="N30" s="11" t="n"/>
       <c r="O30" s="14" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="31">
@@ -1813,34 +1813,34 @@
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1942607</v>
+        <v>2111370</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>3126.6</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>607.3755</v>
+        <v>660.1409</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>3126.6</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>607.3755</v>
+        <v>660.1409</v>
       </c>
       <c r="K31" s="7" t="n">
         <v>3127.9</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>607.628</v>
+        <v>660.4154</v>
       </c>
       <c r="M31" s="9" t="n">
         <v>-0.0416</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>-0.00098</v>
+        <v>-0.00106</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>2.3451</v>
+        <v>2.5488</v>
       </c>
     </row>
     <row r="32">
@@ -1858,14 +1858,14 @@
       <c r="H32" s="11" t="n"/>
       <c r="I32" s="11" t="n"/>
       <c r="J32" s="13" t="n">
-        <v>607.375</v>
+        <v>660.141</v>
       </c>
       <c r="K32" s="11" t="n"/>
       <c r="L32" s="11" t="n"/>
       <c r="M32" s="11" t="n"/>
       <c r="N32" s="11" t="n"/>
       <c r="O32" s="14" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="33">
@@ -1973,34 +1973,34 @@
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2296142</v>
+        <v>2495618</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>2645.2</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>607.3755</v>
+        <v>660.1409</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>2645.2</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>607.3755</v>
+        <v>660.1409</v>
       </c>
       <c r="K35" s="7" t="n">
         <v>2667.5</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>612.4959</v>
+        <v>665.7061</v>
       </c>
       <c r="M35" s="9" t="n">
         <v>-0.836</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>-0.01961</v>
+        <v>-0.02131</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>2.3451</v>
+        <v>2.5488</v>
       </c>
     </row>
     <row r="36">
@@ -2073,14 +2073,14 @@
       <c r="H37" s="11" t="n"/>
       <c r="I37" s="11" t="n"/>
       <c r="J37" s="13" t="n">
-        <v>686.377</v>
+        <v>739.1420000000001</v>
       </c>
       <c r="K37" s="11" t="n"/>
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="11" t="n"/>
       <c r="N37" s="11" t="n"/>
       <c r="O37" s="14" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="38">
@@ -2108,34 +2108,34 @@
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>4802386</v>
+        <v>5219590</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>942.1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>452.4328</v>
+        <v>491.7376</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>942.1</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>452.4328</v>
+        <v>491.7376</v>
       </c>
       <c r="K38" s="7" t="n">
         <v>919.45</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>441.5554</v>
+        <v>479.9152</v>
       </c>
       <c r="M38" s="9" t="n">
         <v>2.4634</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>0.04303</v>
+        <v>0.04677</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>1.7469</v>
+        <v>1.8986</v>
       </c>
     </row>
     <row r="39">
@@ -2153,14 +2153,14 @@
       <c r="H39" s="11" t="n"/>
       <c r="I39" s="11" t="n"/>
       <c r="J39" s="13" t="n">
-        <v>452.433</v>
+        <v>491.738</v>
       </c>
       <c r="K39" s="11" t="n"/>
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="11" t="n"/>
       <c r="N39" s="11" t="n"/>
       <c r="O39" s="14" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="40">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>3217310</v>
+        <v>3496812</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1059.5</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>340.874</v>
+        <v>370.4872</v>
       </c>
       <c r="I40" s="7" t="n">
         <v>1059.5</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>340.874</v>
+        <v>370.4872</v>
       </c>
       <c r="K40" s="7" t="n">
         <v>1089.7</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>350.5903</v>
+        <v>381.0476</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>-2.7714</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>-0.03647</v>
+        <v>-0.03964</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>1.3161</v>
+        <v>1.4305</v>
       </c>
     </row>
     <row r="41">
@@ -2233,14 +2233,14 @@
       <c r="H41" s="11" t="n"/>
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="13" t="n">
-        <v>340.874</v>
+        <v>370.487</v>
       </c>
       <c r="K41" s="11" t="n"/>
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="11" t="n"/>
       <c r="N41" s="11" t="n"/>
       <c r="O41" s="14" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="42">
@@ -2268,34 +2268,34 @@
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>438588</v>
+        <v>476690</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>2684.9</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>117.7565</v>
+        <v>127.9865</v>
       </c>
       <c r="I42" s="7" t="n">
         <v>2684.9</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>117.7565</v>
+        <v>127.9865</v>
       </c>
       <c r="K42" s="7" t="n">
         <v>2746.8</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>120.4714</v>
+        <v>130.9372</v>
       </c>
       <c r="M42" s="9" t="n">
         <v>-2.2535</v>
       </c>
       <c r="N42" s="10" t="n">
-        <v>-0.01025</v>
+        <v>-0.01114</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>0.4547</v>
+        <v>0.4942</v>
       </c>
     </row>
     <row r="43">
@@ -2323,34 +2323,34 @@
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>2135668</v>
+        <v>2321203</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>435.3</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>92.96559999999999</v>
+        <v>101.042</v>
       </c>
       <c r="I43" s="7" t="n">
         <v>435.3</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>92.96559999999999</v>
+        <v>101.042</v>
       </c>
       <c r="K43" s="7" t="n">
         <v>446.05</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>95.2615</v>
+        <v>103.5373</v>
       </c>
       <c r="M43" s="9" t="n">
         <v>-2.41</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>-0.00865</v>
+        <v>-0.0094</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>0.3589</v>
+        <v>0.3901</v>
       </c>
     </row>
     <row r="44">
@@ -2368,14 +2368,14 @@
       <c r="H44" s="11" t="n"/>
       <c r="I44" s="11" t="n"/>
       <c r="J44" s="13" t="n">
-        <v>210.722</v>
+        <v>229.029</v>
       </c>
       <c r="K44" s="11" t="n"/>
       <c r="L44" s="11" t="n"/>
       <c r="M44" s="11" t="n"/>
       <c r="N44" s="11" t="n"/>
       <c r="O44" s="14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="45">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>INE741K01010</t>
+          <t>INE121A01024</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>CreditAccess Grameen Limited</t>
+          <t>Cholamandalam Investment and Finance Company Limited</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2403,34 +2403,34 @@
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>3687704</v>
+        <v>3182365</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>1462.3</v>
+        <v>1799.2</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>539.253</v>
+        <v>572.5711</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>1462.3</v>
+        <v>1799.2</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>539.253</v>
+        <v>572.5711</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>1460.3</v>
+        <v>1792.9</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>538.5154</v>
+        <v>570.5662</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.137</v>
+        <v>0.3514</v>
       </c>
       <c r="N45" s="10" t="n">
-        <v>0.00285</v>
+        <v>0.00777</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>2.0821</v>
+        <v>2.2107</v>
       </c>
     </row>
     <row r="46">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>INE121A01024</t>
+          <t>INE741K01010</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Cholamandalam Investment and Finance Company Limited</t>
+          <t>CreditAccess Grameen Limited</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2458,34 +2458,34 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>2927997</v>
+        <v>3687704</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>1799.2</v>
+        <v>1462.3</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>526.8052</v>
+        <v>539.253</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>1799.2</v>
+        <v>1462.3</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>526.8052</v>
+        <v>539.253</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>1792.9</v>
+        <v>1460.3</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>524.9606</v>
+        <v>538.5154</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>0.3514</v>
+        <v>0.137</v>
       </c>
       <c r="N46" s="10" t="n">
-        <v>0.00715</v>
+        <v>0.00285</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>2.034</v>
+        <v>2.0821</v>
       </c>
     </row>
     <row r="47">
@@ -2513,34 +2513,34 @@
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>8913093</v>
+        <v>9687412</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>299</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>266.5015</v>
+        <v>289.6536</v>
       </c>
       <c r="I47" s="7" t="n">
         <v>299</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>266.5015</v>
+        <v>289.6536</v>
       </c>
       <c r="K47" s="7" t="n">
         <v>296.55</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>264.3178</v>
+        <v>287.2802</v>
       </c>
       <c r="M47" s="9" t="n">
         <v>0.8262</v>
       </c>
       <c r="N47" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.00924</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>1.029</v>
+        <v>1.1184</v>
       </c>
     </row>
     <row r="48">
@@ -2568,34 +2568,34 @@
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>2402678</v>
+        <v>2611409</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1031.8</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>247.9083</v>
+        <v>269.4452</v>
       </c>
       <c r="I48" s="7" t="n">
         <v>1031.8</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>247.9083</v>
+        <v>269.4452</v>
       </c>
       <c r="K48" s="7" t="n">
         <v>1019</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>244.8329</v>
+        <v>266.1026</v>
       </c>
       <c r="M48" s="9" t="n">
         <v>1.2561</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>0.01202</v>
+        <v>0.01307</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>0.9572000000000001</v>
+        <v>1.0403</v>
       </c>
     </row>
     <row r="49">
@@ -2623,34 +2623,34 @@
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1369776</v>
+        <v>1488774</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1764.6</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>241.7107</v>
+        <v>262.7091</v>
       </c>
       <c r="I49" s="7" t="n">
         <v>1764.6</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>241.7107</v>
+        <v>262.7091</v>
       </c>
       <c r="K49" s="7" t="n">
         <v>1780.5</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>243.8886</v>
+        <v>265.0762</v>
       </c>
       <c r="M49" s="9" t="n">
         <v>-0.893</v>
       </c>
       <c r="N49" s="10" t="n">
-        <v>-0.008330000000000001</v>
+        <v>-0.00906</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>0.9332</v>
+        <v>1.0143</v>
       </c>
     </row>
     <row r="50">
@@ -2723,14 +2723,14 @@
       <c r="H51" s="11" t="n"/>
       <c r="I51" s="11" t="n"/>
       <c r="J51" s="13" t="n">
-        <v>1986.241</v>
+        <v>2097.694</v>
       </c>
       <c r="K51" s="11" t="n"/>
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="11" t="n"/>
       <c r="N51" s="11" t="n"/>
       <c r="O51" s="14" t="n">
-        <v>7.67</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="52">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>2715075</v>
+        <v>2950945</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1689.2</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>458.6305</v>
+        <v>498.4736</v>
       </c>
       <c r="I52" s="7" t="n">
         <v>1689.2</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>458.6305</v>
+        <v>498.4736</v>
       </c>
       <c r="K52" s="7" t="n">
         <v>1656.0784</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>449.6377</v>
+        <v>488.6996</v>
       </c>
       <c r="M52" s="9" t="n">
         <v>2</v>
       </c>
       <c r="N52" s="10" t="n">
-        <v>0.03542</v>
+        <v>0.03849</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>1.7708</v>
+        <v>1.9246</v>
       </c>
     </row>
     <row r="53">
@@ -2813,34 +2813,34 @@
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>411161</v>
+        <v>446880</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>8592</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>353.2695</v>
+        <v>383.9593</v>
       </c>
       <c r="I53" s="7" t="n">
         <v>8592</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>353.2695</v>
+        <v>383.9593</v>
       </c>
       <c r="K53" s="7" t="n">
         <v>8573.5</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>352.5089</v>
+        <v>383.1326</v>
       </c>
       <c r="M53" s="9" t="n">
         <v>0.2158</v>
       </c>
       <c r="N53" s="10" t="n">
-        <v>0.00294</v>
+        <v>0.0032</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>1.364</v>
+        <v>1.4825</v>
       </c>
     </row>
     <row r="54">
@@ -2913,14 +2913,14 @@
       <c r="H55" s="11" t="n"/>
       <c r="I55" s="11" t="n"/>
       <c r="J55" s="13" t="n">
-        <v>989.5549999999999</v>
+        <v>1060.088</v>
       </c>
       <c r="K55" s="11" t="n"/>
       <c r="L55" s="11" t="n"/>
       <c r="M55" s="11" t="n"/>
       <c r="N55" s="11" t="n"/>
       <c r="O55" s="14" t="n">
-        <v>3.82</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="56">
@@ -3028,34 +3028,34 @@
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>3320740</v>
+        <v>3609227</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1437.1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>477.2235</v>
+        <v>518.682</v>
       </c>
       <c r="I58" s="7" t="n">
         <v>1437.1</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>477.2235</v>
+        <v>518.682</v>
       </c>
       <c r="K58" s="7" t="n">
         <v>1461.6</v>
       </c>
       <c r="L58" s="8" t="n">
-        <v>485.3594</v>
+        <v>527.5246</v>
       </c>
       <c r="M58" s="9" t="n">
         <v>-1.6762</v>
       </c>
       <c r="N58" s="10" t="n">
-        <v>-0.03089</v>
+        <v>-0.03357</v>
       </c>
       <c r="O58" s="9" t="n">
-        <v>1.8426</v>
+        <v>2.0026</v>
       </c>
     </row>
     <row r="59">
@@ -3083,34 +3083,34 @@
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>3452431</v>
+        <v>3752359</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1041.2</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>359.4671</v>
+        <v>390.6956</v>
       </c>
       <c r="I59" s="7" t="n">
         <v>1041.2</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>359.4671</v>
+        <v>390.6956</v>
       </c>
       <c r="K59" s="7" t="n">
         <v>1056.6</v>
       </c>
       <c r="L59" s="8" t="n">
-        <v>364.7839</v>
+        <v>396.4743</v>
       </c>
       <c r="M59" s="9" t="n">
         <v>-1.4575</v>
       </c>
       <c r="N59" s="10" t="n">
-        <v>-0.02023</v>
+        <v>-0.02199</v>
       </c>
       <c r="O59" s="9" t="n">
-        <v>1.3879</v>
+        <v>1.5085</v>
       </c>
     </row>
     <row r="60">
@@ -3138,34 +3138,34 @@
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>588856</v>
+        <v>640012</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>4841.5</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>285.0946</v>
+        <v>309.8618</v>
       </c>
       <c r="I60" s="7" t="n">
         <v>4841.5</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>285.0946</v>
+        <v>309.8618</v>
       </c>
       <c r="K60" s="7" t="n">
         <v>4928.5</v>
       </c>
       <c r="L60" s="8" t="n">
-        <v>290.2177</v>
+        <v>315.4299</v>
       </c>
       <c r="M60" s="9" t="n">
         <v>-1.7652</v>
       </c>
       <c r="N60" s="10" t="n">
-        <v>-0.01943</v>
+        <v>-0.02112</v>
       </c>
       <c r="O60" s="9" t="n">
-        <v>1.1008</v>
+        <v>1.1964</v>
       </c>
     </row>
     <row r="61">
@@ -3193,34 +3193,34 @@
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1463981</v>
+        <v>1591164</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1100.7</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>161.1404</v>
+        <v>175.1394</v>
       </c>
       <c r="I61" s="7" t="n">
         <v>1100.7</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>161.1404</v>
+        <v>175.1394</v>
       </c>
       <c r="K61" s="7" t="n">
         <v>1113.9</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>163.0728</v>
+        <v>177.2398</v>
       </c>
       <c r="M61" s="9" t="n">
         <v>-1.185</v>
       </c>
       <c r="N61" s="10" t="n">
-        <v>-0.00737</v>
+        <v>-0.00801</v>
       </c>
       <c r="O61" s="9" t="n">
-        <v>0.6222</v>
+        <v>0.6762</v>
       </c>
     </row>
     <row r="62">
@@ -3238,14 +3238,14 @@
       <c r="H62" s="11" t="n"/>
       <c r="I62" s="11" t="n"/>
       <c r="J62" s="13" t="n">
-        <v>1282.926</v>
+        <v>1394.379</v>
       </c>
       <c r="K62" s="11" t="n"/>
       <c r="L62" s="11" t="n"/>
       <c r="M62" s="11" t="n"/>
       <c r="N62" s="11" t="n"/>
       <c r="O62" s="14" t="n">
-        <v>4.95</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="63">
@@ -3273,34 +3273,34 @@
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>78641</v>
+        <v>85473</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>39405</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>309.8849</v>
+        <v>336.8064</v>
       </c>
       <c r="I63" s="7" t="n">
         <v>39405</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>309.8849</v>
+        <v>336.8064</v>
       </c>
       <c r="K63" s="7" t="n">
         <v>39015</v>
       </c>
       <c r="L63" s="8" t="n">
-        <v>306.8179</v>
+        <v>333.4729</v>
       </c>
       <c r="M63" s="9" t="n">
         <v>0.9996</v>
       </c>
       <c r="N63" s="10" t="n">
-        <v>0.01196</v>
+        <v>0.013</v>
       </c>
       <c r="O63" s="9" t="n">
-        <v>1.1965</v>
+        <v>1.3004</v>
       </c>
     </row>
     <row r="64">
@@ -3318,14 +3318,14 @@
       <c r="H64" s="11" t="n"/>
       <c r="I64" s="11" t="n"/>
       <c r="J64" s="13" t="n">
-        <v>309.885</v>
+        <v>336.806</v>
       </c>
       <c r="K64" s="11" t="n"/>
       <c r="L64" s="11" t="n"/>
       <c r="M64" s="11" t="n"/>
       <c r="N64" s="11" t="n"/>
       <c r="O64" s="14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="65">
@@ -3353,34 +3353,34 @@
         </is>
       </c>
       <c r="F65" s="6" t="n">
-        <v>3705592</v>
+        <v>4027513</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1455.1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>539.2007</v>
+        <v>586.0434</v>
       </c>
       <c r="I65" s="7" t="n">
         <v>1455.1</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>539.2007</v>
+        <v>586.0434</v>
       </c>
       <c r="K65" s="7" t="n">
         <v>1406</v>
       </c>
       <c r="L65" s="8" t="n">
-        <v>521.0062</v>
+        <v>566.2683</v>
       </c>
       <c r="M65" s="9" t="n">
         <v>3.4922</v>
       </c>
       <c r="N65" s="10" t="n">
-        <v>0.0727</v>
+        <v>0.07902000000000001</v>
       </c>
       <c r="O65" s="9" t="n">
-        <v>2.0819</v>
+        <v>2.2627</v>
       </c>
     </row>
     <row r="66">
@@ -3408,34 +3408,34 @@
         </is>
       </c>
       <c r="F66" s="6" t="n">
-        <v>2117129</v>
+        <v>2301053</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>2488.3</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>526.8052</v>
+        <v>572.571</v>
       </c>
       <c r="I66" s="7" t="n">
         <v>2488.3</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>526.8052</v>
+        <v>572.571</v>
       </c>
       <c r="K66" s="7" t="n">
         <v>2438</v>
       </c>
       <c r="L66" s="8" t="n">
-        <v>516.1561</v>
+        <v>560.9967</v>
       </c>
       <c r="M66" s="9" t="n">
         <v>2.0632</v>
       </c>
       <c r="N66" s="10" t="n">
-        <v>0.04197</v>
+        <v>0.04561</v>
       </c>
       <c r="O66" s="9" t="n">
-        <v>2.034</v>
+        <v>2.2107</v>
       </c>
     </row>
     <row r="67">
@@ -3463,34 +3463,34 @@
         </is>
       </c>
       <c r="F67" s="6" t="n">
-        <v>3251203</v>
+        <v>3533648</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1486.9</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>483.4214</v>
+        <v>525.4181</v>
       </c>
       <c r="I67" s="7" t="n">
         <v>1486.9</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>483.4214</v>
+        <v>525.4181</v>
       </c>
       <c r="K67" s="7" t="n">
         <v>1536.7</v>
       </c>
       <c r="L67" s="8" t="n">
-        <v>499.6124</v>
+        <v>543.0157</v>
       </c>
       <c r="M67" s="9" t="n">
         <v>-3.2407</v>
       </c>
       <c r="N67" s="10" t="n">
-        <v>-0.06049</v>
+        <v>-0.06574000000000001</v>
       </c>
       <c r="O67" s="9" t="n">
-        <v>1.8665</v>
+        <v>2.0286</v>
       </c>
     </row>
     <row r="68">
@@ -3518,34 +3518,34 @@
         </is>
       </c>
       <c r="F68" s="6" t="n">
-        <v>626142</v>
+        <v>680538</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>5642</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>353.2693</v>
+        <v>383.9595</v>
       </c>
       <c r="I68" s="7" t="n">
         <v>5642</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>353.2693</v>
+        <v>383.9595</v>
       </c>
       <c r="K68" s="7" t="n">
         <v>5555.5</v>
       </c>
       <c r="L68" s="8" t="n">
-        <v>347.8532</v>
+        <v>378.0729</v>
       </c>
       <c r="M68" s="9" t="n">
         <v>1.557</v>
       </c>
       <c r="N68" s="10" t="n">
-        <v>0.02124</v>
+        <v>0.02308</v>
       </c>
       <c r="O68" s="9" t="n">
-        <v>1.364</v>
+        <v>1.4825</v>
       </c>
     </row>
     <row r="69">
@@ -3628,34 +3628,34 @@
         </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1174921</v>
+        <v>1276992</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1793.5</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>210.7221</v>
+        <v>229.0285</v>
       </c>
       <c r="I70" s="7" t="n">
         <v>1793.5</v>
       </c>
       <c r="J70" s="8" t="n">
-        <v>210.7221</v>
+        <v>229.0285</v>
       </c>
       <c r="K70" s="7" t="n">
         <v>1826.2</v>
       </c>
       <c r="L70" s="8" t="n">
-        <v>214.5641</v>
+        <v>233.2043</v>
       </c>
       <c r="M70" s="9" t="n">
         <v>-1.7906</v>
       </c>
       <c r="N70" s="10" t="n">
-        <v>-0.01457</v>
+        <v>-0.01583</v>
       </c>
       <c r="O70" s="9" t="n">
-        <v>0.8136</v>
+        <v>0.8843</v>
       </c>
     </row>
     <row r="71">
@@ -3673,14 +3673,14 @@
       <c r="H71" s="11" t="n"/>
       <c r="I71" s="11" t="n"/>
       <c r="J71" s="13" t="n">
-        <v>2358.563</v>
+        <v>2542.164</v>
       </c>
       <c r="K71" s="11" t="n"/>
       <c r="L71" s="11" t="n"/>
       <c r="M71" s="11" t="n"/>
       <c r="N71" s="11" t="n"/>
       <c r="O71" s="14" t="n">
-        <v>9.109999999999999</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="72">
@@ -3708,34 +3708,34 @@
         </is>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1674502</v>
+        <v>1819974</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1813.6</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>303.6877</v>
+        <v>330.0705</v>
       </c>
       <c r="I72" s="7" t="n">
         <v>1813.6</v>
       </c>
       <c r="J72" s="8" t="n">
-        <v>303.6877</v>
+        <v>330.0705</v>
       </c>
       <c r="K72" s="7" t="n">
         <v>1821.1</v>
       </c>
       <c r="L72" s="8" t="n">
-        <v>304.9436</v>
+        <v>331.4355</v>
       </c>
       <c r="M72" s="9" t="n">
         <v>-0.4118</v>
       </c>
       <c r="N72" s="10" t="n">
-        <v>-0.00483</v>
+        <v>-0.00525</v>
       </c>
       <c r="O72" s="9" t="n">
-        <v>1.1725</v>
+        <v>1.2744</v>
       </c>
     </row>
     <row r="73">
@@ -3763,34 +3763,34 @@
         </is>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1669393</v>
+        <v>1814420</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1744.9</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>291.2924</v>
+        <v>316.5981</v>
       </c>
       <c r="I73" s="7" t="n">
         <v>1744.9</v>
       </c>
       <c r="J73" s="8" t="n">
-        <v>291.2924</v>
+        <v>316.5981</v>
       </c>
       <c r="K73" s="7" t="n">
         <v>1767.7</v>
       </c>
       <c r="L73" s="8" t="n">
-        <v>295.0986</v>
+        <v>320.735</v>
       </c>
       <c r="M73" s="9" t="n">
         <v>-1.2898</v>
       </c>
       <c r="N73" s="10" t="n">
-        <v>-0.01451</v>
+        <v>-0.01577</v>
       </c>
       <c r="O73" s="9" t="n">
-        <v>1.1247</v>
+        <v>1.2224</v>
       </c>
     </row>
     <row r="74">
@@ -3818,34 +3818,34 @@
         </is>
       </c>
       <c r="F74" s="6" t="n">
-        <v>615386</v>
+        <v>668848</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1611.4</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>99.16330000000001</v>
+        <v>107.7782</v>
       </c>
       <c r="I74" s="7" t="n">
         <v>1611.4</v>
       </c>
       <c r="J74" s="8" t="n">
-        <v>99.16330000000001</v>
+        <v>107.7782</v>
       </c>
       <c r="K74" s="7" t="n">
         <v>1662.3</v>
       </c>
       <c r="L74" s="8" t="n">
-        <v>102.2956</v>
+        <v>111.1826</v>
       </c>
       <c r="M74" s="9" t="n">
         <v>-3.062</v>
       </c>
       <c r="N74" s="10" t="n">
-        <v>-0.01172</v>
+        <v>-0.01274</v>
       </c>
       <c r="O74" s="9" t="n">
-        <v>0.3829</v>
+        <v>0.4161</v>
       </c>
     </row>
     <row r="75">
@@ -3863,14 +3863,14 @@
       <c r="H75" s="11" t="n"/>
       <c r="I75" s="11" t="n"/>
       <c r="J75" s="13" t="n">
-        <v>694.143</v>
+        <v>754.447</v>
       </c>
       <c r="K75" s="11" t="n"/>
       <c r="L75" s="11" t="n"/>
       <c r="M75" s="11" t="n"/>
       <c r="N75" s="11" t="n"/>
       <c r="O75" s="14" t="n">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="76">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>4876502</v>
+        <v>5300145</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>953.2</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>464.8282</v>
+        <v>505.2098</v>
       </c>
       <c r="I76" s="7" t="n">
         <v>953.2</v>
       </c>
       <c r="J76" s="8" t="n">
-        <v>464.8282</v>
+        <v>505.2098</v>
       </c>
       <c r="K76" s="7" t="n">
         <v>976.6</v>
       </c>
       <c r="L76" s="8" t="n">
-        <v>476.2392</v>
+        <v>517.6122</v>
       </c>
       <c r="M76" s="9" t="n">
         <v>-2.3961</v>
       </c>
       <c r="N76" s="10" t="n">
-        <v>-0.043</v>
+        <v>-0.04674</v>
       </c>
       <c r="O76" s="9" t="n">
-        <v>1.7947</v>
+        <v>1.9506</v>
       </c>
     </row>
     <row r="77">
@@ -3943,14 +3943,14 @@
       <c r="H77" s="11" t="n"/>
       <c r="I77" s="11" t="n"/>
       <c r="J77" s="13" t="n">
-        <v>464.828</v>
+        <v>505.21</v>
       </c>
       <c r="K77" s="11" t="n"/>
       <c r="L77" s="11" t="n"/>
       <c r="M77" s="11" t="n"/>
       <c r="N77" s="11" t="n"/>
       <c r="O77" s="14" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="78">
@@ -3978,34 +3978,34 @@
         </is>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1976845</v>
+        <v>2148582</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1034.6</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>204.5244</v>
+        <v>222.2923</v>
       </c>
       <c r="I78" s="7" t="n">
         <v>1034.6</v>
       </c>
       <c r="J78" s="8" t="n">
-        <v>204.5244</v>
+        <v>222.2923</v>
       </c>
       <c r="K78" s="7" t="n">
         <v>1020.5</v>
       </c>
       <c r="L78" s="8" t="n">
-        <v>201.737</v>
+        <v>219.2628</v>
       </c>
       <c r="M78" s="9" t="n">
         <v>1.3817</v>
       </c>
       <c r="N78" s="10" t="n">
-        <v>0.01091</v>
+        <v>0.01186</v>
       </c>
       <c r="O78" s="9" t="n">
-        <v>0.7897</v>
+        <v>0.8583</v>
       </c>
     </row>
     <row r="79">
@@ -4023,14 +4023,14 @@
       <c r="H79" s="11" t="n"/>
       <c r="I79" s="11" t="n"/>
       <c r="J79" s="13" t="n">
-        <v>204.524</v>
+        <v>222.292</v>
       </c>
       <c r="K79" s="11" t="n"/>
       <c r="L79" s="11" t="n"/>
       <c r="M79" s="11" t="n"/>
       <c r="N79" s="11" t="n"/>
       <c r="O79" s="14" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="80">
@@ -4058,34 +4058,34 @@
         </is>
       </c>
       <c r="F80" s="6" t="n">
-        <v>2303981</v>
+        <v>2504138</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1318.1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>303.6877</v>
+        <v>330.0704</v>
       </c>
       <c r="I80" s="7" t="n">
         <v>1318.1</v>
       </c>
       <c r="J80" s="8" t="n">
-        <v>303.6877</v>
+        <v>330.0704</v>
       </c>
       <c r="K80" s="7" t="n">
         <v>1313.6</v>
       </c>
       <c r="L80" s="8" t="n">
-        <v>302.6509</v>
+        <v>328.9436</v>
       </c>
       <c r="M80" s="9" t="n">
         <v>0.3426</v>
       </c>
       <c r="N80" s="10" t="n">
-        <v>0.00402</v>
+        <v>0.00437</v>
       </c>
       <c r="O80" s="9" t="n">
-        <v>1.1725</v>
+        <v>1.2744</v>
       </c>
     </row>
     <row r="81">
@@ -4103,14 +4103,14 @@
       <c r="H81" s="11" t="n"/>
       <c r="I81" s="11" t="n"/>
       <c r="J81" s="13" t="n">
-        <v>303.688</v>
+        <v>330.07</v>
       </c>
       <c r="K81" s="11" t="n"/>
       <c r="L81" s="11" t="n"/>
       <c r="M81" s="11" t="n"/>
       <c r="N81" s="11" t="n"/>
       <c r="O81" s="14" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="82">
@@ -4138,34 +4138,34 @@
         </is>
       </c>
       <c r="F82" s="6" t="n">
-        <v>6427977</v>
+        <v>6796196</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>761.7</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>489.619</v>
+        <v>517.6662</v>
       </c>
       <c r="I82" s="7" t="n">
         <v>761.7</v>
       </c>
       <c r="J82" s="8" t="n">
-        <v>489.619</v>
+        <v>517.6662</v>
       </c>
       <c r="K82" s="7" t="n">
         <v>767.0859</v>
       </c>
       <c r="L82" s="8" t="n">
-        <v>493.081</v>
+        <v>521.3266</v>
       </c>
       <c r="M82" s="9" t="n">
         <v>-0.7020999999999999</v>
       </c>
       <c r="N82" s="10" t="n">
-        <v>-0.01327</v>
+        <v>-0.01403</v>
       </c>
       <c r="O82" s="9" t="n">
-        <v>1.8904</v>
+        <v>1.9987</v>
       </c>
     </row>
     <row r="83">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>INE044A01036</t>
+          <t>INE570L01029</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>SAI Life Sciences Ltd</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4193,34 +4193,34 @@
         </is>
       </c>
       <c r="F83" s="6" t="n">
-        <v>1663547</v>
+        <v>2757771</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>1862.8</v>
+        <v>1221.3</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>309.8855</v>
+        <v>336.8066</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>1862.8</v>
+        <v>1221.3</v>
       </c>
       <c r="J83" s="8" t="n">
-        <v>309.8855</v>
+        <v>336.8066</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>1874.4</v>
+        <v>1205</v>
       </c>
       <c r="L83" s="8" t="n">
-        <v>311.8152</v>
+        <v>332.3114</v>
       </c>
       <c r="M83" s="9" t="n">
-        <v>-0.6189</v>
+        <v>1.3527</v>
       </c>
       <c r="N83" s="10" t="n">
-        <v>-0.00741</v>
+        <v>0.01759</v>
       </c>
       <c r="O83" s="9" t="n">
-        <v>1.1965</v>
+        <v>1.3004</v>
       </c>
     </row>
     <row r="84">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>INE570L01029</t>
+          <t>INE044A01036</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>SAI Life Sciences Ltd</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -4248,34 +4248,34 @@
         </is>
       </c>
       <c r="F84" s="6" t="n">
-        <v>2537341</v>
+        <v>1808066</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>1221.3</v>
+        <v>1862.8</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>309.8855</v>
+        <v>336.8065</v>
       </c>
       <c r="I84" s="7" t="n">
-        <v>1221.3</v>
+        <v>1862.8</v>
       </c>
       <c r="J84" s="8" t="n">
-        <v>309.8855</v>
+        <v>336.8065</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>1205</v>
+        <v>1874.4</v>
       </c>
       <c r="L84" s="8" t="n">
-        <v>305.7496</v>
+        <v>338.9039</v>
       </c>
       <c r="M84" s="9" t="n">
-        <v>1.3527</v>
+        <v>-0.6189</v>
       </c>
       <c r="N84" s="10" t="n">
-        <v>0.01619</v>
+        <v>-0.00805</v>
       </c>
       <c r="O84" s="9" t="n">
-        <v>1.1965</v>
+        <v>1.3004</v>
       </c>
     </row>
     <row r="85">
@@ -4303,34 +4303,34 @@
         </is>
       </c>
       <c r="F85" s="6" t="n">
-        <v>981646</v>
+        <v>1066926</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>2462.3</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>241.7107</v>
+        <v>262.7092</v>
       </c>
       <c r="I85" s="7" t="n">
         <v>2462.3</v>
       </c>
       <c r="J85" s="8" t="n">
-        <v>241.7107</v>
+        <v>262.7092</v>
       </c>
       <c r="K85" s="7" t="n">
         <v>2483</v>
       </c>
       <c r="L85" s="8" t="n">
-        <v>243.7427</v>
+        <v>264.9177</v>
       </c>
       <c r="M85" s="9" t="n">
         <v>-0.8337</v>
       </c>
       <c r="N85" s="10" t="n">
-        <v>-0.00778</v>
+        <v>-0.008460000000000001</v>
       </c>
       <c r="O85" s="9" t="n">
-        <v>0.9332</v>
+        <v>1.0143</v>
       </c>
     </row>
     <row r="86">
@@ -4413,34 +4413,34 @@
         </is>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1234762</v>
+        <v>1342031</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>1556</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>192.129</v>
+        <v>208.82</v>
       </c>
       <c r="I87" s="7" t="n">
         <v>1556</v>
       </c>
       <c r="J87" s="8" t="n">
-        <v>192.129</v>
+        <v>208.82</v>
       </c>
       <c r="K87" s="7" t="n">
         <v>1564</v>
       </c>
       <c r="L87" s="8" t="n">
-        <v>193.1168</v>
+        <v>209.8936</v>
       </c>
       <c r="M87" s="9" t="n">
         <v>-0.5115</v>
       </c>
       <c r="N87" s="10" t="n">
-        <v>-0.00379</v>
+        <v>-0.00412</v>
       </c>
       <c r="O87" s="9" t="n">
-        <v>0.7418</v>
+        <v>0.8063</v>
       </c>
     </row>
     <row r="88">
@@ -4458,14 +4458,14 @@
       <c r="H88" s="11" t="n"/>
       <c r="I88" s="11" t="n"/>
       <c r="J88" s="13" t="n">
-        <v>1771.552</v>
+        <v>1891.131</v>
       </c>
       <c r="K88" s="11" t="n"/>
       <c r="L88" s="11" t="n"/>
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
       <c r="O88" s="14" t="n">
-        <v>6.84</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="89">
@@ -4573,34 +4573,34 @@
         </is>
       </c>
       <c r="F91" s="6" t="n">
-        <v>11935066</v>
+        <v>12971916</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>508.9</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>607.3755</v>
+        <v>660.1408</v>
       </c>
       <c r="I91" s="7" t="n">
         <v>508.9</v>
       </c>
       <c r="J91" s="8" t="n">
-        <v>607.3755</v>
+        <v>660.1408</v>
       </c>
       <c r="K91" s="7" t="n">
         <v>516.35</v>
       </c>
       <c r="L91" s="8" t="n">
-        <v>616.2671</v>
+        <v>669.8049</v>
       </c>
       <c r="M91" s="9" t="n">
         <v>-1.4428</v>
       </c>
       <c r="N91" s="10" t="n">
-        <v>-0.03384</v>
+        <v>-0.03677</v>
       </c>
       <c r="O91" s="9" t="n">
-        <v>2.3451</v>
+        <v>2.5488</v>
       </c>
     </row>
     <row r="92">
@@ -4628,34 +4628,34 @@
         </is>
       </c>
       <c r="F92" s="6" t="n">
-        <v>938041</v>
+        <v>1019533</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>4294.6</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>402.8511</v>
+        <v>437.8486</v>
       </c>
       <c r="I92" s="7" t="n">
         <v>4294.6</v>
       </c>
       <c r="J92" s="8" t="n">
-        <v>402.8511</v>
+        <v>437.8486</v>
       </c>
       <c r="K92" s="7" t="n">
         <v>4336</v>
       </c>
       <c r="L92" s="8" t="n">
-        <v>406.7346</v>
+        <v>442.0695</v>
       </c>
       <c r="M92" s="9" t="n">
         <v>-0.9548</v>
       </c>
       <c r="N92" s="10" t="n">
-        <v>-0.01485</v>
+        <v>-0.01614</v>
       </c>
       <c r="O92" s="9" t="n">
-        <v>1.5554</v>
+        <v>1.6905</v>
       </c>
     </row>
     <row r="93">
@@ -4683,34 +4683,34 @@
         </is>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1233298</v>
+        <v>1340440</v>
       </c>
       <c r="G93" s="7" t="n">
         <v>3216.2</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>396.6533</v>
+        <v>431.1123</v>
       </c>
       <c r="I93" s="7" t="n">
         <v>3216.2</v>
       </c>
       <c r="J93" s="8" t="n">
-        <v>396.6533</v>
+        <v>431.1123</v>
       </c>
       <c r="K93" s="7" t="n">
         <v>3247</v>
       </c>
       <c r="L93" s="8" t="n">
-        <v>400.4519</v>
+        <v>435.2409</v>
       </c>
       <c r="M93" s="9" t="n">
         <v>-0.9486</v>
       </c>
       <c r="N93" s="10" t="n">
-        <v>-0.01453</v>
+        <v>-0.01579</v>
       </c>
       <c r="O93" s="9" t="n">
-        <v>1.5315</v>
+        <v>1.6645</v>
       </c>
     </row>
     <row r="94">
@@ -4738,34 +4738,34 @@
         </is>
       </c>
       <c r="F94" s="6" t="n">
-        <v>14331367</v>
+        <v>15576395</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>255.15</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>365.6648</v>
+        <v>397.4317</v>
       </c>
       <c r="I94" s="7" t="n">
         <v>255.15</v>
       </c>
       <c r="J94" s="8" t="n">
-        <v>365.6648</v>
+        <v>397.4317</v>
       </c>
       <c r="K94" s="7" t="n">
         <v>256.35</v>
       </c>
       <c r="L94" s="8" t="n">
-        <v>367.3846</v>
+        <v>399.3009</v>
       </c>
       <c r="M94" s="9" t="n">
         <v>-0.4681</v>
       </c>
       <c r="N94" s="10" t="n">
-        <v>-0.00661</v>
+        <v>-0.00718</v>
       </c>
       <c r="O94" s="9" t="n">
-        <v>1.4118</v>
+        <v>1.5345</v>
       </c>
     </row>
     <row r="95">
@@ -4793,34 +4793,34 @@
         </is>
       </c>
       <c r="F95" s="6" t="n">
-        <v>17285110</v>
+        <v>18786742</v>
       </c>
       <c r="G95" s="7" t="n">
         <v>186.45</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>322.2809</v>
+        <v>350.2788</v>
       </c>
       <c r="I95" s="7" t="n">
         <v>186.45</v>
       </c>
       <c r="J95" s="8" t="n">
-        <v>322.2809</v>
+        <v>350.2788</v>
       </c>
       <c r="K95" s="7" t="n">
         <v>188.37</v>
       </c>
       <c r="L95" s="8" t="n">
-        <v>325.5996</v>
+        <v>353.8859</v>
       </c>
       <c r="M95" s="9" t="n">
         <v>-1.0193</v>
       </c>
       <c r="N95" s="10" t="n">
-        <v>-0.01268</v>
+        <v>-0.01379</v>
       </c>
       <c r="O95" s="9" t="n">
-        <v>1.2443</v>
+        <v>1.3524</v>
       </c>
     </row>
     <row r="96">
@@ -4893,14 +4893,14 @@
       <c r="H97" s="11" t="n"/>
       <c r="I97" s="11" t="n"/>
       <c r="J97" s="13" t="n">
-        <v>2222.663</v>
+        <v>2404.649</v>
       </c>
       <c r="K97" s="11" t="n"/>
       <c r="L97" s="11" t="n"/>
       <c r="M97" s="11" t="n"/>
       <c r="N97" s="11" t="n"/>
       <c r="O97" s="14" t="n">
-        <v>8.58</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -4928,34 +4928,34 @@
         </is>
       </c>
       <c r="F98" s="6" t="n">
-        <v>2009308</v>
+        <v>2183865</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>1850.7</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>371.8626</v>
+        <v>404.1679</v>
       </c>
       <c r="I98" s="7" t="n">
         <v>1850.7</v>
       </c>
       <c r="J98" s="8" t="n">
-        <v>371.8626</v>
+        <v>404.1679</v>
       </c>
       <c r="K98" s="7" t="n">
         <v>1877.3</v>
       </c>
       <c r="L98" s="8" t="n">
-        <v>377.2074</v>
+        <v>409.977</v>
       </c>
       <c r="M98" s="9" t="n">
         <v>-1.4169</v>
       </c>
       <c r="N98" s="10" t="n">
-        <v>-0.02034</v>
+        <v>-0.02211</v>
       </c>
       <c r="O98" s="9" t="n">
-        <v>1.4358</v>
+        <v>1.5605</v>
       </c>
     </row>
     <row r="99">
@@ -4973,14 +4973,14 @@
       <c r="H99" s="11" t="n"/>
       <c r="I99" s="11" t="n"/>
       <c r="J99" s="13" t="n">
-        <v>371.863</v>
+        <v>404.168</v>
       </c>
       <c r="K99" s="11" t="n"/>
       <c r="L99" s="11" t="n"/>
       <c r="M99" s="11" t="n"/>
       <c r="N99" s="11" t="n"/>
       <c r="O99" s="14" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="100">
@@ -5008,34 +5008,34 @@
         </is>
       </c>
       <c r="F100" s="6" t="n">
-        <v>21146739</v>
+        <v>22983847</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>108.44</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>229.3152</v>
+        <v>249.2368</v>
       </c>
       <c r="I100" s="7" t="n">
         <v>108.44</v>
       </c>
       <c r="J100" s="8" t="n">
-        <v>229.3152</v>
+        <v>249.2368</v>
       </c>
       <c r="K100" s="7" t="n">
         <v>108.07</v>
       </c>
       <c r="L100" s="8" t="n">
-        <v>228.5328</v>
+        <v>248.3864</v>
       </c>
       <c r="M100" s="9" t="n">
         <v>0.3424</v>
       </c>
       <c r="N100" s="10" t="n">
-        <v>0.00303</v>
+        <v>0.00329</v>
       </c>
       <c r="O100" s="9" t="n">
-        <v>0.8854</v>
+        <v>0.9623</v>
       </c>
     </row>
     <row r="101">
@@ -5063,34 +5063,34 @@
         </is>
       </c>
       <c r="F101" s="6" t="n">
-        <v>517626</v>
+        <v>562594</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>1796</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>92.96559999999999</v>
+        <v>101.0419</v>
       </c>
       <c r="I101" s="7" t="n">
         <v>1796</v>
       </c>
       <c r="J101" s="8" t="n">
-        <v>92.96559999999999</v>
+        <v>101.0419</v>
       </c>
       <c r="K101" s="7" t="n">
         <v>1813.3</v>
       </c>
       <c r="L101" s="8" t="n">
-        <v>93.86109999999999</v>
+        <v>102.0152</v>
       </c>
       <c r="M101" s="9" t="n">
         <v>-0.9540999999999999</v>
       </c>
       <c r="N101" s="10" t="n">
-        <v>-0.00342</v>
+        <v>-0.00372</v>
       </c>
       <c r="O101" s="9" t="n">
-        <v>0.3589</v>
+        <v>0.3901</v>
       </c>
     </row>
     <row r="102">
@@ -5108,14 +5108,14 @@
       <c r="H102" s="11" t="n"/>
       <c r="I102" s="11" t="n"/>
       <c r="J102" s="13" t="n">
-        <v>322.281</v>
+        <v>350.279</v>
       </c>
       <c r="K102" s="11" t="n"/>
       <c r="L102" s="11" t="n"/>
       <c r="M102" s="11" t="n"/>
       <c r="N102" s="11" t="n"/>
       <c r="O102" s="14" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="104">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="C104" s="15" t="n">
-        <v>22824.834</v>
+        <v>24604.905</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -5140,11 +5140,11 @@
         </is>
       </c>
       <c r="C105" s="15" t="n">
-        <v>3075.066</v>
+        <v>1294.995</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>₹cr (11.87%)</t>
+          <t>₹cr (5.0%)</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>-0.1378</v>
+        <v>-0.1433</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/amc_book/Aditya Birla Sun Life Mutual Fund/Aditya Birla SL Flexi Cap Fund _G_/FACT_SHEET_2026-06-25.xlsx
+++ b/amc_book/Aditya Birla Sun Life Mutual Fund/Aditya Birla SL Flexi Cap Fund _G_/FACT_SHEET_2026-06-25.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -618,34 +618,34 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3691683</v>
+        <v>3149018</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1131.3</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>417.6401</v>
+        <v>356.2484</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>1131.3</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>417.6401</v>
+        <v>356.2484</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>1098.1</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>405.3837</v>
+        <v>345.7937</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>3.0234</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>0.04875</v>
+        <v>0.04159</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1.6125</v>
+        <v>1.3755</v>
       </c>
     </row>
     <row r="7">
@@ -663,14 +663,14 @@
       <c r="H7" s="11" t="n"/>
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="13" t="n">
-        <v>417.64</v>
+        <v>356.248</v>
       </c>
       <c r="K7" s="11" t="n"/>
       <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="14" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="8">
@@ -698,34 +698,34 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>2637556</v>
+        <v>2684770</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>2145.3</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>565.8348999999999</v>
+        <v>575.9637</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>2145.3</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>565.8348999999999</v>
+        <v>575.9637</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>2122.8</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>559.9004</v>
+        <v>569.923</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>1.0599</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>0.02316</v>
+        <v>0.02357</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>2.1847</v>
+        <v>2.2238</v>
       </c>
     </row>
     <row r="9">
@@ -753,34 +753,34 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1210238</v>
+        <v>1867465</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>2616</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>316.5983</v>
+        <v>488.5288</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>2616</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>316.5983</v>
+        <v>488.5288</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>2660</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>321.9233</v>
+        <v>496.7457</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>-1.6541</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>-0.02022</v>
+        <v>-0.0312</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>1.2224</v>
+        <v>1.8862</v>
       </c>
     </row>
     <row r="10">
@@ -789,12 +789,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>INE974X01010</t>
+          <t>INE073K01018</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Tube Investments of India Limited</t>
+          <t>Sona BLW Precision Forgings Limited</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -804,38 +804,38 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>970497</v>
+        <v>5765384</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>3054</v>
+        <v>619.25</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>296.3898</v>
+        <v>357.0214</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>3054</v>
+        <v>619.25</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>296.3898</v>
+        <v>357.0214</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>3170.5</v>
+        <v>619.2999</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>307.6961</v>
+        <v>357.0501</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>-3.6745</v>
+        <v>-0.0081</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>-0.04205</v>
+        <v>-0.00011</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>1.1444</v>
+        <v>1.3785</v>
       </c>
     </row>
     <row r="11">
@@ -844,12 +844,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>INE073K01018</t>
+          <t>INE974X01010</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Sona BLW Precision Forgings Limited</t>
+          <t>Tube Investments of India Limited</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -859,38 +859,38 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>3263366</v>
+        <v>1050181</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>619.25</v>
+        <v>3054</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>202.0839</v>
+        <v>320.7253</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>619.25</v>
+        <v>3054</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>202.0839</v>
+        <v>320.7253</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>619.2999</v>
+        <v>3170.5</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>202.1002</v>
+        <v>332.9599</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>-0.0081</v>
+        <v>-3.6745</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>-6e-05</v>
+        <v>-0.0455</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>0.7802</v>
+        <v>1.2383</v>
       </c>
     </row>
     <row r="12">
@@ -908,14 +908,14 @@
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="13" t="n">
-        <v>1380.907</v>
+        <v>1742.239</v>
       </c>
       <c r="K12" s="11" t="n"/>
       <c r="L12" s="11" t="n"/>
       <c r="M12" s="11" t="n"/>
       <c r="N12" s="11" t="n"/>
       <c r="O12" s="14" t="n">
-        <v>5.33</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="13">
@@ -924,12 +924,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>INE917I01010</t>
+          <t>INE0LEZ01016</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Bajaj Auto Limited</t>
+          <t>Ather Energy Ltd</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -939,38 +939,38 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>568017</v>
+        <v>5173642</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>9843</v>
+        <v>998.75</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>559.0991</v>
+        <v>516.7175</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>9843</v>
+        <v>998.75</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>559.0991</v>
+        <v>516.7175</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>9750</v>
+        <v>990.1</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>553.8166</v>
+        <v>512.2423</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.9538</v>
+        <v>0.8736</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>0.02059</v>
+        <v>0.01743</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>2.1587</v>
+        <v>1.9951</v>
       </c>
     </row>
     <row r="14">
@@ -979,12 +979,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>INE101A01026</t>
+          <t>INE917I01010</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Limited</t>
+          <t>Bajaj Auto Limited</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -994,38 +994,38 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1185417</v>
+        <v>505478</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>3182.2</v>
+        <v>9843</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>377.2234</v>
+        <v>497.542</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>3182.2</v>
+        <v>9843</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>377.2234</v>
+        <v>497.542</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>3064.5</v>
+        <v>9750</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>363.271</v>
+        <v>492.841</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>3.8408</v>
+        <v>0.9538</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>0.05594</v>
+        <v>0.01832</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>1.4565</v>
+        <v>1.921</v>
       </c>
     </row>
     <row r="15">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>INE0LEZ01016</t>
+          <t>INE101A01026</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Ather Energy Ltd</t>
+          <t>Mahindra &amp; Mahindra Limited</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1053,34 +1053,34 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>3709509</v>
+        <v>880526</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>998.75</v>
+        <v>3182.2</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>370.4872</v>
+        <v>280.201</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>998.75</v>
+        <v>3182.2</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>370.4872</v>
+        <v>280.201</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>990.1</v>
+        <v>3064.5</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>367.2785</v>
+        <v>269.8372</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.8736</v>
+        <v>3.8408</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.04155</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>1.4305</v>
+        <v>1.0819</v>
       </c>
     </row>
     <row r="16">
@@ -1108,34 +1108,34 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>196031</v>
+        <v>162695</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>13745</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>269.4446</v>
+        <v>223.6243</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>13745</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>269.4446</v>
+        <v>223.6243</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>13248</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>259.7019</v>
+        <v>215.5383</v>
       </c>
       <c r="M16" s="9" t="n">
         <v>3.7515</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>0.03903</v>
+        <v>0.03239</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>1.0403</v>
+        <v>0.8633999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1153,14 +1153,14 @@
       <c r="H17" s="11" t="n"/>
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="13" t="n">
-        <v>1576.254</v>
+        <v>1518.085</v>
       </c>
       <c r="K17" s="11" t="n"/>
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="11" t="n"/>
       <c r="O17" s="14" t="n">
-        <v>6.09</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="18">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>INE949L01017</t>
+          <t>INE171A01029</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Limited</t>
+          <t>The Federal Bank Limited</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1184,38 +1184,38 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>5082151</v>
+        <v>12868326</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1033.85</v>
+        <v>324.05</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>525.4182</v>
+        <v>416.9981</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1033.85</v>
+        <v>324.05</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>525.4182</v>
+        <v>416.9981</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1067.2</v>
+        <v>325.2</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>542.3672</v>
+        <v>418.478</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>-3.125</v>
+        <v>-0.3536</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>-0.06339</v>
+        <v>-0.00569</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>2.0286</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="19">
@@ -1243,34 +1243,34 @@
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>3032531</v>
+        <v>2997297</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1377.2</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>417.6402</v>
+        <v>412.7877</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>1377.2</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>417.6402</v>
+        <v>412.7877</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>1384.5</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>419.8539</v>
+        <v>414.9758</v>
       </c>
       <c r="M19" s="9" t="n">
         <v>-0.5273</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>1.6125</v>
+        <v>1.5938</v>
       </c>
     </row>
     <row r="20">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>INE090A01021</t>
+          <t>INE949L01017</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>AU Small Finance Bank Limited</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1294,38 +1294,38 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>2961470</v>
+        <v>3874165</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>1387.5</v>
+        <v>1033.85</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>410.904</v>
+        <v>400.5305</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1387.5</v>
+        <v>1033.85</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>410.904</v>
+        <v>400.5305</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1373.6</v>
+        <v>1067.2</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>406.7875</v>
+        <v>413.4509</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>1.0119</v>
+        <v>-3.125</v>
       </c>
       <c r="N20" s="10" t="n">
-        <v>0.01605</v>
+        <v>-0.04833</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>1.5865</v>
+        <v>1.5465</v>
       </c>
     </row>
     <row r="21">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>INE237A01036</t>
+          <t>INE062A01020</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1353,34 +1353,34 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>9552459</v>
+        <v>3529149</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>409</v>
+        <v>1045.4</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>390.6956</v>
+        <v>368.9372</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>409</v>
+        <v>1045.4</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>390.6956</v>
+        <v>368.9372</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>405.95</v>
+        <v>1034.6</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>387.7821</v>
+        <v>365.1258</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.7513</v>
+        <v>1.0439</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>0.01133</v>
+        <v>0.01487</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>1.5085</v>
+        <v>1.4245</v>
       </c>
     </row>
     <row r="22">
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>INE171A01029</t>
+          <t>INE090A01021</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>The Federal Bank Limited</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1408,34 +1408,34 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>9770040</v>
+        <v>2534821</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>324.05</v>
+        <v>1387.5</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>316.5981</v>
+        <v>351.7064</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>324.05</v>
+        <v>1387.5</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>316.5981</v>
+        <v>351.7064</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>325.2</v>
+        <v>1373.6</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>317.7217</v>
+        <v>348.183</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>-0.3536</v>
+        <v>1.0119</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>-0.00432</v>
+        <v>0.01374</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>1.2224</v>
+        <v>1.3579</v>
       </c>
     </row>
     <row r="23">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>INE040A01034</t>
+          <t>INE237A01036</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>HDFC Bank Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1463,34 +1463,34 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>3891272</v>
+        <v>8492130</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>796.3</v>
+        <v>409</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>309.862</v>
+        <v>347.3281</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>796.3</v>
+        <v>409</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>309.862</v>
+        <v>347.3281</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>793.2</v>
+        <v>405.95</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>308.6557</v>
+        <v>344.738</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.3908</v>
+        <v>0.7513</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>0.00468</v>
+        <v>0.01007</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>1.1964</v>
+        <v>1.341</v>
       </c>
     </row>
     <row r="24">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>INE062A01020</t>
+          <t>INE040A01034</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>HDFC Bank Limited</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1518,34 +1518,34 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>2770744</v>
+        <v>3142542</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>1045.4</v>
+        <v>796.3</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>289.6536</v>
+        <v>250.2406</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1045.4</v>
+        <v>796.3</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>289.6536</v>
+        <v>250.2406</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>1034.6</v>
+        <v>793.2</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>286.6612</v>
+        <v>249.2664</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>1.0439</v>
+        <v>0.3908</v>
       </c>
       <c r="N24" s="10" t="n">
-        <v>0.01167</v>
+        <v>0.00378</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>1.1184</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1563,14 +1563,14 @@
       <c r="H25" s="11" t="n"/>
       <c r="I25" s="11" t="n"/>
       <c r="J25" s="13" t="n">
-        <v>2660.772</v>
+        <v>2548.529</v>
       </c>
       <c r="K25" s="11" t="n"/>
       <c r="L25" s="11" t="n"/>
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
       <c r="O25" s="14" t="n">
-        <v>10.27</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="26">
@@ -1598,274 +1598,274 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1336743</v>
+        <v>1072318</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>3829.8</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>511.9458</v>
+        <v>410.6763</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>3829.8</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>511.9458</v>
+        <v>410.6763</v>
       </c>
       <c r="K26" s="7" t="n">
         <v>3757.7</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>502.3079</v>
+        <v>402.9449</v>
       </c>
       <c r="M26" s="9" t="n">
         <v>1.9187</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>0.03793</v>
+        <v>0.03042</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>1.9766</v>
+        <v>1.5856</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Beverages — subtotal</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="13" t="n">
+        <v>410.676</v>
+      </c>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="11" t="n"/>
+      <c r="N27" s="11" t="n"/>
+      <c r="O27" s="14" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>INE854D01024</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>United Spirits Limited</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>cyclical</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>1264636</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>1384.9</v>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>175.1394</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>1384.9</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>175.1394</v>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>1359.1</v>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>171.8767</v>
-      </c>
-      <c r="M27" s="9" t="n">
-        <v>1.8983</v>
-      </c>
-      <c r="N27" s="10" t="n">
-        <v>0.01284</v>
-      </c>
-      <c r="O27" s="9" t="n">
-        <v>0.6762</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Beverages — subtotal</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="11" t="n"/>
-      <c r="I28" s="11" t="n"/>
-      <c r="J28" s="13" t="n">
-        <v>687.085</v>
-      </c>
-      <c r="K28" s="11" t="n"/>
-      <c r="L28" s="11" t="n"/>
-      <c r="M28" s="11" t="n"/>
-      <c r="N28" s="11" t="n"/>
-      <c r="O28" s="14" t="n">
-        <v>2.65</v>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>INE732I01021</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>ANGEL ONE LIMITED</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>16159234</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>335.25</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>541.7383</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>335.25</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>541.7383</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>340.65</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>550.4643</v>
+      </c>
+      <c r="M28" s="9" t="n">
+        <v>-1.5852</v>
+      </c>
+      <c r="N28" s="10" t="n">
+        <v>-0.03316</v>
+      </c>
+      <c r="O28" s="9" t="n">
+        <v>2.0917</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Capital Markets — subtotal</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="13" t="n">
+        <v>541.7380000000001</v>
+      </c>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="11" t="n"/>
+      <c r="N29" s="11" t="n"/>
+      <c r="O29" s="14" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>INE732I01021</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>ANGEL ONE LIMITED</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>INE047A01021</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Grasim Industries Limited</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Cement &amp; Cement Products</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>tactical</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1733207</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>3126.6</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>541.9045</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>3126.6</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>541.9045</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>3127.9</v>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>542.1298</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>-0.0416</v>
+      </c>
+      <c r="N30" s="10" t="n">
+        <v>-0.00087</v>
+      </c>
+      <c r="O30" s="9" t="n">
+        <v>2.0923</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Cement &amp; Cement Products — subtotal</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="13" t="n">
+        <v>541.904</v>
+      </c>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n"/>
+      <c r="N31" s="11" t="n"/>
+      <c r="O31" s="14" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>INE100A01010</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Atul Limited</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Chemicals &amp; Petrochemicals</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F29" s="6" t="n">
-        <v>14667786</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>335.25</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>491.7375</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>335.25</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>491.7375</v>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>340.65</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>499.6581</v>
-      </c>
-      <c r="M29" s="9" t="n">
-        <v>-1.5852</v>
-      </c>
-      <c r="N29" s="10" t="n">
-        <v>-0.0301</v>
-      </c>
-      <c r="O29" s="9" t="n">
-        <v>1.8986</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Capital Markets — subtotal</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="11" t="n"/>
-      <c r="I30" s="11" t="n"/>
-      <c r="J30" s="13" t="n">
-        <v>491.738</v>
-      </c>
-      <c r="K30" s="11" t="n"/>
-      <c r="L30" s="11" t="n"/>
-      <c r="M30" s="11" t="n"/>
-      <c r="N30" s="11" t="n"/>
-      <c r="O30" s="14" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>INE047A01021</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Grasim Industries Limited</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Cement &amp; Cement Products</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>tactical</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>2111370</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>3126.6</v>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>660.1409</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>3126.6</v>
-      </c>
-      <c r="J31" s="8" t="n">
-        <v>660.1409</v>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>3127.9</v>
-      </c>
-      <c r="L31" s="8" t="n">
-        <v>660.4154</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>-0.0416</v>
-      </c>
-      <c r="N31" s="10" t="n">
-        <v>-0.00106</v>
-      </c>
-      <c r="O31" s="9" t="n">
-        <v>2.5488</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Cement &amp; Cement Products — subtotal</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="13" t="n">
-        <v>660.141</v>
-      </c>
-      <c r="K32" s="11" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
-      <c r="N32" s="11" t="n"/>
-      <c r="O32" s="14" t="n">
-        <v>2.55</v>
+      <c r="F32" s="6" t="n">
+        <v>334175</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>6670.5</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>222.9114</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>6670.5</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>222.9114</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>6612.5</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>220.9732</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>0.8771</v>
+      </c>
+      <c r="N32" s="10" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>0.8607</v>
       </c>
     </row>
     <row r="33">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>INE100A01010</t>
+          <t>INE647A01010</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Atul Limited</t>
+          <t>SRF Limited</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1889,38 +1889,38 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>334175</v>
+        <v>752537</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>6670.5</v>
+        <v>2732.9</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>222.9114</v>
+        <v>205.6608</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>6670.5</v>
+        <v>2732.9</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>222.9114</v>
+        <v>205.6608</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>6612.5</v>
+        <v>2765.8</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>220.9732</v>
+        <v>208.1367</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.8771</v>
+        <v>-1.1895</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>0.00755</v>
+        <v>-0.00945</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>0.8607</v>
+        <v>0.7941</v>
       </c>
     </row>
     <row r="34">
@@ -1938,14 +1938,14 @@
       <c r="H34" s="11" t="n"/>
       <c r="I34" s="11" t="n"/>
       <c r="J34" s="13" t="n">
-        <v>222.911</v>
+        <v>428.572</v>
       </c>
       <c r="K34" s="11" t="n"/>
       <c r="L34" s="11" t="n"/>
       <c r="M34" s="11" t="n"/>
       <c r="N34" s="11" t="n"/>
       <c r="O34" s="14" t="n">
-        <v>0.86</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="35">
@@ -1954,133 +1954,133 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
+          <t>INE018A01030</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Larsen &amp; Toubro Limited</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>cyclical</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>540409</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>4216.4</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>227.8581</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>4216.4</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>227.8581</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>4181.7</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>225.9828</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>0.8298</v>
+      </c>
+      <c r="N35" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>0.8798</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Construction — subtotal</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n"/>
+      <c r="I36" s="11" t="n"/>
+      <c r="J36" s="13" t="n">
+        <v>227.858</v>
+      </c>
+      <c r="K36" s="11" t="n"/>
+      <c r="L36" s="11" t="n"/>
+      <c r="M36" s="11" t="n"/>
+      <c r="N36" s="11" t="n"/>
+      <c r="O36" s="14" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
           <t>INE021A01026</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Asian Paints Limited</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>tactical</t>
         </is>
       </c>
-      <c r="F35" s="6" t="n">
-        <v>2495618</v>
-      </c>
-      <c r="G35" s="7" t="n">
+      <c r="F37" s="6" t="n">
+        <v>1501015</v>
+      </c>
+      <c r="G37" s="7" t="n">
         <v>2645.2</v>
       </c>
-      <c r="H35" s="8" t="n">
-        <v>660.1409</v>
-      </c>
-      <c r="I35" s="7" t="n">
+      <c r="H37" s="8" t="n">
+        <v>397.0485</v>
+      </c>
+      <c r="I37" s="7" t="n">
         <v>2645.2</v>
       </c>
-      <c r="J35" s="8" t="n">
-        <v>660.1409</v>
-      </c>
-      <c r="K35" s="7" t="n">
+      <c r="J37" s="8" t="n">
+        <v>397.0485</v>
+      </c>
+      <c r="K37" s="7" t="n">
         <v>2667.5</v>
       </c>
-      <c r="L35" s="8" t="n">
-        <v>665.7061</v>
-      </c>
-      <c r="M35" s="9" t="n">
+      <c r="L37" s="8" t="n">
+        <v>400.3958</v>
+      </c>
+      <c r="M37" s="9" t="n">
         <v>-0.836</v>
       </c>
-      <c r="N35" s="10" t="n">
-        <v>-0.02131</v>
-      </c>
-      <c r="O35" s="9" t="n">
-        <v>2.5488</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>INE951I01027</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>V-Guard Industries Limited</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Consumer Durables</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>2580052</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>306.2</v>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>79.0012</v>
-      </c>
-      <c r="I36" s="7" t="n">
-        <v>306.2</v>
-      </c>
-      <c r="J36" s="8" t="n">
-        <v>79.0012</v>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>313.55</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>80.89749999999999</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>-2.3441</v>
-      </c>
-      <c r="N36" s="10" t="n">
-        <v>-0.00715</v>
-      </c>
-      <c r="O36" s="9" t="n">
-        <v>0.305</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Consumer Durables — subtotal</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="13" t="n">
-        <v>739.1420000000001</v>
-      </c>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="n"/>
-      <c r="N37" s="11" t="n"/>
-      <c r="O37" s="14" t="n">
-        <v>2.85</v>
+      <c r="N37" s="10" t="n">
+        <v>-0.01282</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>1.533</v>
       </c>
     </row>
     <row r="38">
@@ -2089,17 +2089,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>INE067A01029</t>
+          <t>INE951I01027</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Limited</t>
+          <t>V-Guard Industries Limited</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2108,34 +2108,34 @@
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>5219590</v>
+        <v>2580052</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>942.1</v>
+        <v>306.2</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>491.7376</v>
+        <v>79.0012</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>942.1</v>
+        <v>306.2</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>491.7376</v>
+        <v>79.0012</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>919.45</v>
+        <v>313.55</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>479.9152</v>
+        <v>80.89749999999999</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>2.4634</v>
+        <v>-2.3441</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>0.04677</v>
+        <v>-0.00715</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>1.8986</v>
+        <v>0.305</v>
       </c>
     </row>
     <row r="39">
@@ -2143,7 +2143,7 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Electrical Equipment — subtotal</t>
+          <t>Consumer Durables — subtotal</t>
         </is>
       </c>
       <c r="D39" s="11" t="n"/>
@@ -2153,14 +2153,14 @@
       <c r="H39" s="11" t="n"/>
       <c r="I39" s="11" t="n"/>
       <c r="J39" s="13" t="n">
-        <v>491.738</v>
+        <v>476.05</v>
       </c>
       <c r="K39" s="11" t="n"/>
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="11" t="n"/>
       <c r="N39" s="11" t="n"/>
       <c r="O39" s="14" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="40">
@@ -2169,17 +2169,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>INE749A01030</t>
+          <t>INE067A01029</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Jindal Steel &amp; Power Limited</t>
+          <t>CG Power and Industrial Solutions Limited</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Ferrous Metals</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>3496812</v>
+        <v>5260647</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>1059.5</v>
+        <v>942.1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>370.4872</v>
+        <v>495.6056</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1059.5</v>
+        <v>942.1</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>370.4872</v>
+        <v>495.6056</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>1089.7</v>
+        <v>919.45</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>381.0476</v>
+        <v>483.6902</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>-2.7714</v>
+        <v>2.4634</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>-0.03964</v>
+        <v>0.04714</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>1.4305</v>
+        <v>1.9135</v>
       </c>
     </row>
     <row r="41">
@@ -2223,7 +2223,7 @@
       <c r="B41" s="11" t="n"/>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Ferrous Metals — subtotal</t>
+          <t>Electrical Equipment — subtotal</t>
         </is>
       </c>
       <c r="D41" s="11" t="n"/>
@@ -2233,14 +2233,14 @@
       <c r="H41" s="11" t="n"/>
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="13" t="n">
-        <v>370.487</v>
+        <v>495.606</v>
       </c>
       <c r="K41" s="11" t="n"/>
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="11" t="n"/>
       <c r="N41" s="11" t="n"/>
       <c r="O41" s="14" t="n">
-        <v>1.43</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="42">
@@ -2249,193 +2249,163 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>INE603J01030</t>
+          <t>INE749A01030</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>PI Industries Litmited</t>
+          <t>Jindal Steel &amp; Power Limited</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>Ferrous Metals</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>4333135</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>1059.5</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>459.0957</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>1059.5</v>
+      </c>
+      <c r="J42" s="8" t="n">
+        <v>459.0957</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>1089.7</v>
+      </c>
+      <c r="L42" s="8" t="n">
+        <v>472.1817</v>
+      </c>
+      <c r="M42" s="9" t="n">
+        <v>-2.7714</v>
+      </c>
+      <c r="N42" s="10" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>1.7726</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Ferrous Metals — subtotal</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="13" t="n">
+        <v>459.096</v>
+      </c>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="11" t="n"/>
+      <c r="M43" s="11" t="n"/>
+      <c r="N43" s="11" t="n"/>
+      <c r="O43" s="14" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>INE258G01013</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Sumitomo Chemical India Limited</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
           <t>Fertilizers &amp; Agrochemicals</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>cyclical</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n">
-        <v>476690</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>2684.9</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>127.9865</v>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>2684.9</v>
-      </c>
-      <c r="J42" s="8" t="n">
-        <v>127.9865</v>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>2746.8</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>130.9372</v>
-      </c>
-      <c r="M42" s="9" t="n">
-        <v>-2.2535</v>
-      </c>
-      <c r="N42" s="10" t="n">
-        <v>-0.01114</v>
-      </c>
-      <c r="O42" s="9" t="n">
-        <v>0.4942</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>INE258G01013</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Sumitomo Chemical India Limited</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Fertilizers &amp; Agrochemicals</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>cyclical</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>2321203</v>
-      </c>
-      <c r="G43" s="7" t="n">
+      <c r="F44" s="6" t="n">
+        <v>4267667</v>
+      </c>
+      <c r="G44" s="7" t="n">
         <v>435.3</v>
       </c>
-      <c r="H43" s="8" t="n">
-        <v>101.042</v>
-      </c>
-      <c r="I43" s="7" t="n">
+      <c r="H44" s="8" t="n">
+        <v>185.7715</v>
+      </c>
+      <c r="I44" s="7" t="n">
         <v>435.3</v>
       </c>
-      <c r="J43" s="8" t="n">
-        <v>101.042</v>
-      </c>
-      <c r="K43" s="7" t="n">
+      <c r="J44" s="8" t="n">
+        <v>185.7715</v>
+      </c>
+      <c r="K44" s="7" t="n">
         <v>446.05</v>
       </c>
-      <c r="L43" s="8" t="n">
-        <v>103.5373</v>
-      </c>
-      <c r="M43" s="9" t="n">
+      <c r="L44" s="8" t="n">
+        <v>190.3593</v>
+      </c>
+      <c r="M44" s="9" t="n">
         <v>-2.41</v>
       </c>
-      <c r="N43" s="10" t="n">
-        <v>-0.0094</v>
-      </c>
-      <c r="O43" s="9" t="n">
-        <v>0.3901</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="N44" s="10" t="n">
+        <v>-0.01729</v>
+      </c>
+      <c r="O44" s="9" t="n">
+        <v>0.7173</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>Fertilizers &amp; Agrochemicals — subtotal</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="11" t="n"/>
-      <c r="I44" s="11" t="n"/>
-      <c r="J44" s="13" t="n">
-        <v>229.029</v>
-      </c>
-      <c r="K44" s="11" t="n"/>
-      <c r="L44" s="11" t="n"/>
-      <c r="M44" s="11" t="n"/>
-      <c r="N44" s="11" t="n"/>
-      <c r="O44" s="14" t="n">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>INE121A01024</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Cholamandalam Investment and Finance Company Limited</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>tactical</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>3182365</v>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>1799.2</v>
-      </c>
-      <c r="H45" s="8" t="n">
-        <v>572.5711</v>
-      </c>
-      <c r="I45" s="7" t="n">
-        <v>1799.2</v>
-      </c>
-      <c r="J45" s="8" t="n">
-        <v>572.5711</v>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>1792.9</v>
-      </c>
-      <c r="L45" s="8" t="n">
-        <v>570.5662</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>0.3514</v>
-      </c>
-      <c r="N45" s="10" t="n">
-        <v>0.00777</v>
-      </c>
-      <c r="O45" s="9" t="n">
-        <v>2.2107</v>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="13" t="n">
+        <v>185.772</v>
+      </c>
+      <c r="K45" s="11" t="n"/>
+      <c r="L45" s="11" t="n"/>
+      <c r="M45" s="11" t="n"/>
+      <c r="N45" s="11" t="n"/>
+      <c r="O45" s="14" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
@@ -2458,48 +2428,48 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>3687704</v>
+        <v>2918661</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1462.3</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>539.253</v>
+        <v>426.7958</v>
       </c>
       <c r="I46" s="7" t="n">
         <v>1462.3</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>539.253</v>
+        <v>426.7958</v>
       </c>
       <c r="K46" s="7" t="n">
         <v>1460.3</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>538.5154</v>
+        <v>426.2121</v>
       </c>
       <c r="M46" s="9" t="n">
         <v>0.137</v>
       </c>
       <c r="N46" s="10" t="n">
-        <v>0.00285</v>
+        <v>0.00226</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>2.0821</v>
+        <v>1.6479</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>INE498L01015</t>
+          <t>INE721A01047</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>L&amp;T Finance Limited</t>
+          <t>Shriram Finance Ltd</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2513,48 +2483,48 @@
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>9687412</v>
+        <v>3809367</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>299</v>
+        <v>1031.8</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>289.6536</v>
+        <v>393.0505</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>299</v>
+        <v>1031.8</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>289.6536</v>
+        <v>393.0505</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>296.55</v>
+        <v>1019</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>287.2802</v>
+        <v>388.1745</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.8262</v>
+        <v>1.2561</v>
       </c>
       <c r="N47" s="10" t="n">
-        <v>0.00924</v>
+        <v>0.01906</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>1.1184</v>
+        <v>1.5176</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>INE721A01047</t>
+          <t>INE121A01024</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Shriram Finance Ltd</t>
+          <t>Cholamandalam Investment and Finance Company Limited</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2564,52 +2534,52 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>2611409</v>
+        <v>2161818</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>1031.8</v>
+        <v>1799.2</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>269.4452</v>
+        <v>388.9543</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1031.8</v>
+        <v>1799.2</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>269.4452</v>
+        <v>388.9543</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>1019</v>
+        <v>1792.9</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>266.1026</v>
+        <v>387.5923</v>
       </c>
       <c r="M48" s="9" t="n">
-        <v>1.2561</v>
+        <v>0.3514</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>0.01307</v>
+        <v>0.00528</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>1.0403</v>
+        <v>1.5018</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>INE918I01026</t>
+          <t>INE498L01015</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Limited</t>
+          <t>L&amp;T Finance Limited</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -2619,178 +2589,178 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1488774</v>
+        <v>10427603</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>1764.6</v>
+        <v>299</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>262.7091</v>
+        <v>311.7853</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1764.6</v>
+        <v>299</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>262.7091</v>
+        <v>311.7853</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>1780.5</v>
+        <v>296.55</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>265.0762</v>
+        <v>309.2306</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>-0.893</v>
+        <v>0.8262</v>
       </c>
       <c r="N49" s="10" t="n">
-        <v>-0.00906</v>
+        <v>0.009950000000000001</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>1.0143</v>
+        <v>1.2038</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>INE918I01026</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Bajaj Finserv Limited</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>cyclical</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>1373721</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>1764.6</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>242.4068</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>1764.6</v>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>242.4068</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>1780.5</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>244.591</v>
+      </c>
+      <c r="M50" s="9" t="n">
+        <v>-0.893</v>
+      </c>
+      <c r="N50" s="10" t="n">
+        <v>-0.008359999999999999</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>0.9359</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>INE423Y01016</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>SBFC Finance Ltd</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F51" s="6" t="n">
         <v>18064555</v>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G51" s="7" t="n">
         <v>90.81999999999999</v>
       </c>
-      <c r="H50" s="8" t="n">
+      <c r="H51" s="8" t="n">
         <v>164.0623</v>
       </c>
-      <c r="I50" s="7" t="n">
+      <c r="I51" s="7" t="n">
         <v>90.81999999999999</v>
       </c>
-      <c r="J50" s="8" t="n">
+      <c r="J51" s="8" t="n">
         <v>164.0623</v>
       </c>
-      <c r="K50" s="7" t="n">
+      <c r="K51" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="L50" s="8" t="n">
+      <c r="L51" s="8" t="n">
         <v>166.1939</v>
       </c>
-      <c r="M50" s="9" t="n">
+      <c r="M51" s="9" t="n">
         <v>-1.2826</v>
       </c>
-      <c r="N50" s="10" t="n">
+      <c r="N51" s="10" t="n">
         <v>-0.00812</v>
       </c>
-      <c r="O50" s="9" t="n">
+      <c r="O51" s="9" t="n">
         <v>0.6334</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="n"/>
-      <c r="B51" s="11" t="n"/>
-      <c r="C51" s="12" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>Finance — subtotal</t>
         </is>
       </c>
-      <c r="D51" s="11" t="n"/>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="11" t="n"/>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="11" t="n"/>
-      <c r="I51" s="11" t="n"/>
-      <c r="J51" s="13" t="n">
-        <v>2097.694</v>
-      </c>
-      <c r="K51" s="11" t="n"/>
-      <c r="L51" s="11" t="n"/>
-      <c r="M51" s="11" t="n"/>
-      <c r="N51" s="11" t="n"/>
-      <c r="O51" s="14" t="n">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>INE600L01024</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Dr. Lal Path Labs Limited</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Healthcare Services</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>2950945</v>
-      </c>
-      <c r="G52" s="7" t="n">
-        <v>1689.2</v>
-      </c>
-      <c r="H52" s="8" t="n">
-        <v>498.4736</v>
-      </c>
-      <c r="I52" s="7" t="n">
-        <v>1689.2</v>
-      </c>
-      <c r="J52" s="8" t="n">
-        <v>498.4736</v>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>1656.0784</v>
-      </c>
-      <c r="L52" s="8" t="n">
-        <v>488.6996</v>
-      </c>
-      <c r="M52" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N52" s="10" t="n">
-        <v>0.03849</v>
-      </c>
-      <c r="O52" s="9" t="n">
-        <v>1.9246</v>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="11" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="11" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="13" t="n">
+        <v>1927.055</v>
+      </c>
+      <c r="K52" s="11" t="n"/>
+      <c r="L52" s="11" t="n"/>
+      <c r="M52" s="11" t="n"/>
+      <c r="N52" s="11" t="n"/>
+      <c r="O52" s="14" t="n">
+        <v>7.44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
@@ -2813,263 +2783,263 @@
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>446880</v>
+        <v>465763</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>8592</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>383.9593</v>
+        <v>400.1836</v>
       </c>
       <c r="I53" s="7" t="n">
         <v>8592</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>383.9593</v>
+        <v>400.1836</v>
       </c>
       <c r="K53" s="7" t="n">
         <v>8573.5</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>383.1326</v>
+        <v>399.3219</v>
       </c>
       <c r="M53" s="9" t="n">
         <v>0.2158</v>
       </c>
       <c r="N53" s="10" t="n">
-        <v>0.0032</v>
+        <v>0.00333</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>1.4825</v>
+        <v>1.5451</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>INE600L01024</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Lal Path Labs Limited</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare Services</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>2291700</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>1689.2</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>387.114</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>1689.2</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>387.114</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>1656.0784</v>
+      </c>
+      <c r="L54" s="8" t="n">
+        <v>379.5235</v>
+      </c>
+      <c r="M54" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" s="10" t="n">
+        <v>0.02989</v>
+      </c>
+      <c r="O54" s="9" t="n">
+        <v>1.4947</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>INE112L01020</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>METROPOLIS HEALTHCARE LIMITED</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Healthcare Services</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F55" s="6" t="n">
         <v>3269628</v>
       </c>
-      <c r="G54" s="7" t="n">
+      <c r="G55" s="7" t="n">
         <v>543.35</v>
       </c>
-      <c r="H54" s="8" t="n">
+      <c r="H55" s="8" t="n">
         <v>177.6552</v>
       </c>
-      <c r="I54" s="7" t="n">
+      <c r="I55" s="7" t="n">
         <v>543.35</v>
       </c>
-      <c r="J54" s="8" t="n">
+      <c r="J55" s="8" t="n">
         <v>177.6552</v>
       </c>
-      <c r="K54" s="7" t="n">
+      <c r="K55" s="7" t="n">
         <v>553.2</v>
       </c>
-      <c r="L54" s="8" t="n">
+      <c r="L55" s="8" t="n">
         <v>180.8758</v>
       </c>
-      <c r="M54" s="9" t="n">
+      <c r="M55" s="9" t="n">
         <v>-1.7805</v>
       </c>
-      <c r="N54" s="10" t="n">
+      <c r="N55" s="10" t="n">
         <v>-0.01221</v>
       </c>
-      <c r="O54" s="9" t="n">
+      <c r="O55" s="9" t="n">
         <v>0.6859</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="11" t="n"/>
-      <c r="B55" s="11" t="n"/>
-      <c r="C55" s="12" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="11" t="n"/>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>Healthcare Services — subtotal</t>
         </is>
       </c>
-      <c r="D55" s="11" t="n"/>
-      <c r="E55" s="11" t="n"/>
-      <c r="F55" s="11" t="n"/>
-      <c r="G55" s="11" t="n"/>
-      <c r="H55" s="11" t="n"/>
-      <c r="I55" s="11" t="n"/>
-      <c r="J55" s="13" t="n">
-        <v>1060.088</v>
-      </c>
-      <c r="K55" s="11" t="n"/>
-      <c r="L55" s="11" t="n"/>
-      <c r="M55" s="11" t="n"/>
-      <c r="N55" s="11" t="n"/>
-      <c r="O55" s="14" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="11" t="n"/>
+      <c r="G56" s="11" t="n"/>
+      <c r="H56" s="11" t="n"/>
+      <c r="I56" s="11" t="n"/>
+      <c r="J56" s="13" t="n">
+        <v>964.953</v>
+      </c>
+      <c r="K56" s="11" t="n"/>
+      <c r="L56" s="11" t="n"/>
+      <c r="M56" s="11" t="n"/>
+      <c r="N56" s="11" t="n"/>
+      <c r="O56" s="14" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>INE121R01077</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>AMAGI MEDIA LABS LTD</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>IT - Services</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>tactical</t>
         </is>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F57" s="6" t="n">
         <v>3038832</v>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="G57" s="7" t="n">
         <v>514.05</v>
       </c>
-      <c r="H56" s="8" t="n">
+      <c r="H57" s="8" t="n">
         <v>156.2112</v>
       </c>
-      <c r="I56" s="7" t="n">
+      <c r="I57" s="7" t="n">
         <v>514.05</v>
       </c>
-      <c r="J56" s="8" t="n">
+      <c r="J57" s="8" t="n">
         <v>156.2112</v>
       </c>
-      <c r="K56" s="7" t="n">
+      <c r="K57" s="7" t="n">
         <v>533.2</v>
       </c>
-      <c r="L56" s="8" t="n">
+      <c r="L57" s="8" t="n">
         <v>162.0305</v>
       </c>
-      <c r="M56" s="9" t="n">
+      <c r="M57" s="9" t="n">
         <v>-3.5915</v>
       </c>
-      <c r="N56" s="10" t="n">
+      <c r="N57" s="10" t="n">
         <v>-0.02166</v>
       </c>
-      <c r="O56" s="9" t="n">
+      <c r="O57" s="9" t="n">
         <v>0.6031</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="11" t="n"/>
-      <c r="B57" s="11" t="n"/>
-      <c r="C57" s="12" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="11" t="n"/>
+      <c r="B58" s="11" t="n"/>
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>IT - Services — subtotal</t>
         </is>
       </c>
-      <c r="D57" s="11" t="n"/>
-      <c r="E57" s="11" t="n"/>
-      <c r="F57" s="11" t="n"/>
-      <c r="G57" s="11" t="n"/>
-      <c r="H57" s="11" t="n"/>
-      <c r="I57" s="11" t="n"/>
-      <c r="J57" s="13" t="n">
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="11" t="n"/>
+      <c r="F58" s="11" t="n"/>
+      <c r="G58" s="11" t="n"/>
+      <c r="H58" s="11" t="n"/>
+      <c r="I58" s="11" t="n"/>
+      <c r="J58" s="13" t="n">
         <v>156.211</v>
       </c>
-      <c r="K57" s="11" t="n"/>
-      <c r="L57" s="11" t="n"/>
-      <c r="M57" s="11" t="n"/>
-      <c r="N57" s="11" t="n"/>
-      <c r="O57" s="14" t="n">
+      <c r="K58" s="11" t="n"/>
+      <c r="L58" s="11" t="n"/>
+      <c r="M58" s="11" t="n"/>
+      <c r="N58" s="11" t="n"/>
+      <c r="O58" s="14" t="n">
         <v>0.6</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>INE669C01036</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Tech Mahindra Limited</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>IT - Software</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>tactical</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>3609227</v>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>1437.1</v>
-      </c>
-      <c r="H58" s="8" t="n">
-        <v>518.682</v>
-      </c>
-      <c r="I58" s="7" t="n">
-        <v>1437.1</v>
-      </c>
-      <c r="J58" s="8" t="n">
-        <v>518.682</v>
-      </c>
-      <c r="K58" s="7" t="n">
-        <v>1461.6</v>
-      </c>
-      <c r="L58" s="8" t="n">
-        <v>527.5246</v>
-      </c>
-      <c r="M58" s="9" t="n">
-        <v>-1.6762</v>
-      </c>
-      <c r="N58" s="10" t="n">
-        <v>-0.03357</v>
-      </c>
-      <c r="O58" s="9" t="n">
-        <v>2.0026</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>INE009A01021</t>
+          <t>INE669C01036</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Tech Mahindra Limited</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -3079,52 +3049,52 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>3752359</v>
+        <v>2667128</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>1041.2</v>
+        <v>1437.1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>390.6956</v>
+        <v>383.293</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>1041.2</v>
+        <v>1437.1</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>390.6956</v>
+        <v>383.293</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>1056.6</v>
+        <v>1461.6</v>
       </c>
       <c r="L59" s="8" t="n">
-        <v>396.4743</v>
+        <v>389.8274</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>-1.4575</v>
+        <v>-1.6762</v>
       </c>
       <c r="N59" s="10" t="n">
-        <v>-0.02199</v>
+        <v>-0.02481</v>
       </c>
       <c r="O59" s="9" t="n">
-        <v>1.5085</v>
+        <v>1.4799</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>INE262H01021</t>
+          <t>INE009A01021</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Persistent Systems Limited</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3138,48 +3108,48 @@
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>640012</v>
+        <v>2464334</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>4841.5</v>
+        <v>1041.2</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>309.8618</v>
+        <v>256.5865</v>
       </c>
       <c r="I60" s="7" t="n">
-        <v>4841.5</v>
+        <v>1041.2</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>309.8618</v>
+        <v>256.5865</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>4928.5</v>
+        <v>1056.6</v>
       </c>
       <c r="L60" s="8" t="n">
-        <v>315.4299</v>
+        <v>260.3815</v>
       </c>
       <c r="M60" s="9" t="n">
-        <v>-1.7652</v>
+        <v>-1.4575</v>
       </c>
       <c r="N60" s="10" t="n">
-        <v>-0.02112</v>
+        <v>-0.01444</v>
       </c>
       <c r="O60" s="9" t="n">
-        <v>1.1964</v>
+        <v>0.9907</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>INE860A01027</t>
+          <t>INE262H01021</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>Persistent Systems Limited</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3189,38 +3159,38 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1591164</v>
+        <v>419001</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>1100.7</v>
+        <v>4841.5</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>175.1394</v>
+        <v>202.8593</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>1100.7</v>
+        <v>4841.5</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>175.1394</v>
+        <v>202.8593</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>1113.9</v>
+        <v>4928.5</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>177.2398</v>
+        <v>206.5046</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>-1.185</v>
+        <v>-1.7652</v>
       </c>
       <c r="N61" s="10" t="n">
-        <v>-0.00801</v>
+        <v>-0.01383</v>
       </c>
       <c r="O61" s="9" t="n">
-        <v>0.6762</v>
+        <v>0.7832</v>
       </c>
     </row>
     <row r="62">
@@ -3238,19 +3208,19 @@
       <c r="H62" s="11" t="n"/>
       <c r="I62" s="11" t="n"/>
       <c r="J62" s="13" t="n">
-        <v>1394.379</v>
+        <v>842.739</v>
       </c>
       <c r="K62" s="11" t="n"/>
       <c r="L62" s="11" t="n"/>
       <c r="M62" s="11" t="n"/>
       <c r="N62" s="11" t="n"/>
       <c r="O62" s="14" t="n">
-        <v>5.38</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
@@ -3273,34 +3243,34 @@
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>85473</v>
+        <v>82603</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>39405</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>336.8064</v>
+        <v>325.4971</v>
       </c>
       <c r="I63" s="7" t="n">
         <v>39405</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>336.8064</v>
+        <v>325.4971</v>
       </c>
       <c r="K63" s="7" t="n">
         <v>39015</v>
       </c>
       <c r="L63" s="8" t="n">
-        <v>333.4729</v>
+        <v>322.2756</v>
       </c>
       <c r="M63" s="9" t="n">
         <v>0.9996</v>
       </c>
       <c r="N63" s="10" t="n">
-        <v>0.013</v>
+        <v>0.01256</v>
       </c>
       <c r="O63" s="9" t="n">
-        <v>1.3004</v>
+        <v>1.2568</v>
       </c>
     </row>
     <row r="64">
@@ -3318,19 +3288,19 @@
       <c r="H64" s="11" t="n"/>
       <c r="I64" s="11" t="n"/>
       <c r="J64" s="13" t="n">
-        <v>336.806</v>
+        <v>325.497</v>
       </c>
       <c r="K64" s="11" t="n"/>
       <c r="L64" s="11" t="n"/>
       <c r="M64" s="11" t="n"/>
       <c r="N64" s="11" t="n"/>
       <c r="O64" s="14" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
@@ -3353,39 +3323,39 @@
         </is>
       </c>
       <c r="F65" s="6" t="n">
-        <v>4027513</v>
+        <v>4662538</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1455.1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>586.0434</v>
+        <v>678.4459000000001</v>
       </c>
       <c r="I65" s="7" t="n">
         <v>1455.1</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>586.0434</v>
+        <v>678.4459000000001</v>
       </c>
       <c r="K65" s="7" t="n">
         <v>1406</v>
       </c>
       <c r="L65" s="8" t="n">
-        <v>566.2683</v>
+        <v>655.5528</v>
       </c>
       <c r="M65" s="9" t="n">
         <v>3.4922</v>
       </c>
       <c r="N65" s="10" t="n">
-        <v>0.07902000000000001</v>
+        <v>0.09148000000000001</v>
       </c>
       <c r="O65" s="9" t="n">
-        <v>2.2627</v>
+        <v>2.6195</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
@@ -3408,48 +3378,48 @@
         </is>
       </c>
       <c r="F66" s="6" t="n">
-        <v>2301053</v>
+        <v>2535013</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>2488.3</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>572.571</v>
+        <v>630.7873</v>
       </c>
       <c r="I66" s="7" t="n">
         <v>2488.3</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>572.571</v>
+        <v>630.7873</v>
       </c>
       <c r="K66" s="7" t="n">
         <v>2438</v>
       </c>
       <c r="L66" s="8" t="n">
-        <v>560.9967</v>
+        <v>618.0362</v>
       </c>
       <c r="M66" s="9" t="n">
         <v>2.0632</v>
       </c>
       <c r="N66" s="10" t="n">
-        <v>0.04561</v>
+        <v>0.05025</v>
       </c>
       <c r="O66" s="9" t="n">
-        <v>2.2107</v>
+        <v>2.4355</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>INE006I01046</t>
+          <t>INE298A01020</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Astral Limited</t>
+          <t>Cummins India Limited</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3459,52 +3429,52 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F67" s="6" t="n">
-        <v>3533648</v>
+        <v>796510</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>1486.9</v>
+        <v>5642</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>525.4181</v>
+        <v>449.3909</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>1486.9</v>
+        <v>5642</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>525.4181</v>
+        <v>449.3909</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>1536.7</v>
+        <v>5555.5</v>
       </c>
       <c r="L67" s="8" t="n">
-        <v>543.0157</v>
+        <v>442.5011</v>
       </c>
       <c r="M67" s="9" t="n">
-        <v>-3.2407</v>
+        <v>1.557</v>
       </c>
       <c r="N67" s="10" t="n">
-        <v>-0.06574000000000001</v>
+        <v>0.02702</v>
       </c>
       <c r="O67" s="9" t="n">
-        <v>2.0286</v>
+        <v>1.7351</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>INE298A01020</t>
+          <t>INE006I01046</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Cummins India Limited</t>
+          <t>Astral Limited</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3514,52 +3484,52 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F68" s="6" t="n">
-        <v>680538</v>
+        <v>2768473</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>5642</v>
+        <v>1486.9</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>383.9595</v>
+        <v>411.6443</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>5642</v>
+        <v>1486.9</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>383.9595</v>
+        <v>411.6443</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>5555.5</v>
+        <v>1536.7</v>
       </c>
       <c r="L68" s="8" t="n">
-        <v>378.0729</v>
+        <v>425.4312</v>
       </c>
       <c r="M68" s="9" t="n">
-        <v>1.557</v>
+        <v>-3.2407</v>
       </c>
       <c r="N68" s="10" t="n">
-        <v>0.02308</v>
+        <v>-0.05151</v>
       </c>
       <c r="O68" s="9" t="n">
-        <v>1.4825</v>
+        <v>1.5894</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>INE330T01021</t>
+          <t>INE702C01027</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Happy Forgings Ltd</t>
+          <t>APL Apollo Tubes Limited</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -3569,52 +3539,52 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1624223</v>
+        <v>1872164</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>1509.3</v>
+        <v>1793.5</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>245.144</v>
+        <v>335.7726</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>1509.3</v>
+        <v>1793.5</v>
       </c>
       <c r="J69" s="8" t="n">
-        <v>245.144</v>
+        <v>335.7726</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>1528.8</v>
+        <v>1826.2</v>
       </c>
       <c r="L69" s="8" t="n">
-        <v>248.3112</v>
+        <v>341.8946</v>
       </c>
       <c r="M69" s="9" t="n">
-        <v>-1.2755</v>
+        <v>-1.7906</v>
       </c>
       <c r="N69" s="10" t="n">
-        <v>-0.01207</v>
+        <v>-0.02321</v>
       </c>
       <c r="O69" s="9" t="n">
-        <v>0.9465</v>
+        <v>1.2964</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>INE702C01027</t>
+          <t>INE330T01021</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>APL Apollo Tubes Limited</t>
+          <t>Happy Forgings Ltd</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3624,38 +3594,38 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1276992</v>
+        <v>1624223</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>1793.5</v>
+        <v>1509.3</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>229.0285</v>
+        <v>245.144</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>1793.5</v>
+        <v>1509.3</v>
       </c>
       <c r="J70" s="8" t="n">
-        <v>229.0285</v>
+        <v>245.144</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>1826.2</v>
+        <v>1528.8</v>
       </c>
       <c r="L70" s="8" t="n">
-        <v>233.2043</v>
+        <v>248.3112</v>
       </c>
       <c r="M70" s="9" t="n">
-        <v>-1.7906</v>
+        <v>-1.2755</v>
       </c>
       <c r="N70" s="10" t="n">
-        <v>-0.01583</v>
+        <v>-0.01207</v>
       </c>
       <c r="O70" s="9" t="n">
-        <v>0.8843</v>
+        <v>0.9465</v>
       </c>
     </row>
     <row r="71">
@@ -3673,19 +3643,19 @@
       <c r="H71" s="11" t="n"/>
       <c r="I71" s="11" t="n"/>
       <c r="J71" s="13" t="n">
-        <v>2542.164</v>
+        <v>2751.185</v>
       </c>
       <c r="K71" s="11" t="n"/>
       <c r="L71" s="11" t="n"/>
       <c r="M71" s="11" t="n"/>
       <c r="N71" s="11" t="n"/>
       <c r="O71" s="14" t="n">
-        <v>9.81</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
@@ -3708,39 +3678,39 @@
         </is>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1819974</v>
+        <v>1626197</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1813.6</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>330.0705</v>
+        <v>294.9271</v>
       </c>
       <c r="I72" s="7" t="n">
         <v>1813.6</v>
       </c>
       <c r="J72" s="8" t="n">
-        <v>330.0705</v>
+        <v>294.9271</v>
       </c>
       <c r="K72" s="7" t="n">
         <v>1821.1</v>
       </c>
       <c r="L72" s="8" t="n">
-        <v>331.4355</v>
+        <v>296.1467</v>
       </c>
       <c r="M72" s="9" t="n">
         <v>-0.4118</v>
       </c>
       <c r="N72" s="10" t="n">
-        <v>-0.00525</v>
+        <v>-0.00469</v>
       </c>
       <c r="O72" s="9" t="n">
-        <v>1.2744</v>
+        <v>1.1387</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
@@ -3763,39 +3733,39 @@
         </is>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1814420</v>
+        <v>1689179</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1744.9</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>316.5981</v>
+        <v>294.7448</v>
       </c>
       <c r="I73" s="7" t="n">
         <v>1744.9</v>
       </c>
       <c r="J73" s="8" t="n">
-        <v>316.5981</v>
+        <v>294.7448</v>
       </c>
       <c r="K73" s="7" t="n">
         <v>1767.7</v>
       </c>
       <c r="L73" s="8" t="n">
-        <v>320.735</v>
+        <v>298.5962</v>
       </c>
       <c r="M73" s="9" t="n">
         <v>-1.2898</v>
       </c>
       <c r="N73" s="10" t="n">
-        <v>-0.01577</v>
+        <v>-0.01468</v>
       </c>
       <c r="O73" s="9" t="n">
-        <v>1.2224</v>
+        <v>1.138</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
@@ -3818,34 +3788,34 @@
         </is>
       </c>
       <c r="F74" s="6" t="n">
-        <v>668848</v>
+        <v>1440100</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1611.4</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>107.7782</v>
+        <v>232.0577</v>
       </c>
       <c r="I74" s="7" t="n">
         <v>1611.4</v>
       </c>
       <c r="J74" s="8" t="n">
-        <v>107.7782</v>
+        <v>232.0577</v>
       </c>
       <c r="K74" s="7" t="n">
         <v>1662.3</v>
       </c>
       <c r="L74" s="8" t="n">
-        <v>111.1826</v>
+        <v>239.3878</v>
       </c>
       <c r="M74" s="9" t="n">
         <v>-3.062</v>
       </c>
       <c r="N74" s="10" t="n">
-        <v>-0.01274</v>
+        <v>-0.02744</v>
       </c>
       <c r="O74" s="9" t="n">
-        <v>0.4161</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="75">
@@ -3863,19 +3833,19 @@
       <c r="H75" s="11" t="n"/>
       <c r="I75" s="11" t="n"/>
       <c r="J75" s="13" t="n">
-        <v>754.447</v>
+        <v>821.73</v>
       </c>
       <c r="K75" s="11" t="n"/>
       <c r="L75" s="11" t="n"/>
       <c r="M75" s="11" t="n"/>
       <c r="N75" s="11" t="n"/>
       <c r="O75" s="14" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
@@ -3898,34 +3868,34 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>5300145</v>
+        <v>6908776</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>953.2</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>505.2098</v>
+        <v>658.5445</v>
       </c>
       <c r="I76" s="7" t="n">
         <v>953.2</v>
       </c>
       <c r="J76" s="8" t="n">
-        <v>505.2098</v>
+        <v>658.5445</v>
       </c>
       <c r="K76" s="7" t="n">
         <v>976.6</v>
       </c>
       <c r="L76" s="8" t="n">
-        <v>517.6122</v>
+        <v>674.7111</v>
       </c>
       <c r="M76" s="9" t="n">
         <v>-2.3961</v>
       </c>
       <c r="N76" s="10" t="n">
-        <v>-0.04674</v>
+        <v>-0.06093</v>
       </c>
       <c r="O76" s="9" t="n">
-        <v>1.9506</v>
+        <v>2.5427</v>
       </c>
     </row>
     <row r="77">
@@ -3943,19 +3913,19 @@
       <c r="H77" s="11" t="n"/>
       <c r="I77" s="11" t="n"/>
       <c r="J77" s="13" t="n">
-        <v>505.21</v>
+        <v>658.544</v>
       </c>
       <c r="K77" s="11" t="n"/>
       <c r="L77" s="11" t="n"/>
       <c r="M77" s="11" t="n"/>
       <c r="N77" s="11" t="n"/>
       <c r="O77" s="14" t="n">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
@@ -3978,34 +3948,34 @@
         </is>
       </c>
       <c r="F78" s="6" t="n">
-        <v>2148582</v>
+        <v>2131582</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1034.6</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>222.2923</v>
+        <v>220.5335</v>
       </c>
       <c r="I78" s="7" t="n">
         <v>1034.6</v>
       </c>
       <c r="J78" s="8" t="n">
-        <v>222.2923</v>
+        <v>220.5335</v>
       </c>
       <c r="K78" s="7" t="n">
         <v>1020.5</v>
       </c>
       <c r="L78" s="8" t="n">
-        <v>219.2628</v>
+        <v>217.5279</v>
       </c>
       <c r="M78" s="9" t="n">
         <v>1.3817</v>
       </c>
       <c r="N78" s="10" t="n">
-        <v>0.01186</v>
+        <v>0.01177</v>
       </c>
       <c r="O78" s="9" t="n">
-        <v>0.8583</v>
+        <v>0.8515</v>
       </c>
     </row>
     <row r="79">
@@ -4023,163 +3993,163 @@
       <c r="H79" s="11" t="n"/>
       <c r="I79" s="11" t="n"/>
       <c r="J79" s="13" t="n">
-        <v>222.292</v>
+        <v>220.534</v>
       </c>
       <c r="K79" s="11" t="n"/>
       <c r="L79" s="11" t="n"/>
       <c r="M79" s="11" t="n"/>
       <c r="N79" s="11" t="n"/>
       <c r="O79" s="14" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>INE094A01015</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Hindustan Petroleum Corporation Limited</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Petroleum Products</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>cyclical</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>8511442</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>409.25</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>348.3308</v>
+      </c>
+      <c r="I80" s="7" t="n">
+        <v>409.25</v>
+      </c>
+      <c r="J80" s="8" t="n">
+        <v>348.3308</v>
+      </c>
+      <c r="K80" s="7" t="n">
+        <v>412.9</v>
+      </c>
+      <c r="L80" s="8" t="n">
+        <v>351.4374</v>
+      </c>
+      <c r="M80" s="9" t="n">
+        <v>-0.884</v>
+      </c>
+      <c r="N80" s="10" t="n">
+        <v>-0.01189</v>
+      </c>
+      <c r="O80" s="9" t="n">
+        <v>1.3449</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>INE002A01018</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>Reliance Industries Limited</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>Petroleum Products</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F80" s="6" t="n">
-        <v>2504138</v>
-      </c>
-      <c r="G80" s="7" t="n">
+      <c r="F81" s="6" t="n">
+        <v>2257573</v>
+      </c>
+      <c r="G81" s="7" t="n">
         <v>1318.1</v>
       </c>
-      <c r="H80" s="8" t="n">
-        <v>330.0704</v>
-      </c>
-      <c r="I80" s="7" t="n">
+      <c r="H81" s="8" t="n">
+        <v>297.5707</v>
+      </c>
+      <c r="I81" s="7" t="n">
         <v>1318.1</v>
       </c>
-      <c r="J80" s="8" t="n">
-        <v>330.0704</v>
-      </c>
-      <c r="K80" s="7" t="n">
+      <c r="J81" s="8" t="n">
+        <v>297.5707</v>
+      </c>
+      <c r="K81" s="7" t="n">
         <v>1313.6</v>
       </c>
-      <c r="L80" s="8" t="n">
-        <v>328.9436</v>
-      </c>
-      <c r="M80" s="9" t="n">
+      <c r="L81" s="8" t="n">
+        <v>296.5548</v>
+      </c>
+      <c r="M81" s="9" t="n">
         <v>0.3426</v>
       </c>
-      <c r="N80" s="10" t="n">
-        <v>0.00437</v>
-      </c>
-      <c r="O80" s="9" t="n">
-        <v>1.2744</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="11" t="n"/>
-      <c r="B81" s="11" t="n"/>
-      <c r="C81" s="12" t="inlineStr">
+      <c r="N81" s="10" t="n">
+        <v>0.00394</v>
+      </c>
+      <c r="O81" s="9" t="n">
+        <v>1.1489</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="n"/>
+      <c r="B82" s="11" t="n"/>
+      <c r="C82" s="12" t="inlineStr">
         <is>
           <t>Petroleum Products — subtotal</t>
         </is>
       </c>
-      <c r="D81" s="11" t="n"/>
-      <c r="E81" s="11" t="n"/>
-      <c r="F81" s="11" t="n"/>
-      <c r="G81" s="11" t="n"/>
-      <c r="H81" s="11" t="n"/>
-      <c r="I81" s="11" t="n"/>
-      <c r="J81" s="13" t="n">
-        <v>330.07</v>
-      </c>
-      <c r="K81" s="11" t="n"/>
-      <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
-      <c r="N81" s="11" t="n"/>
-      <c r="O81" s="14" t="n">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>INE0CZ201020</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>ANTHEM BIOSCIENCES LIMITED</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>tactical</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>6796196</v>
-      </c>
-      <c r="G82" s="7" t="n">
-        <v>761.7</v>
-      </c>
-      <c r="H82" s="8" t="n">
-        <v>517.6662</v>
-      </c>
-      <c r="I82" s="7" t="n">
-        <v>761.7</v>
-      </c>
-      <c r="J82" s="8" t="n">
-        <v>517.6662</v>
-      </c>
-      <c r="K82" s="7" t="n">
-        <v>767.0859</v>
-      </c>
-      <c r="L82" s="8" t="n">
-        <v>521.3266</v>
-      </c>
-      <c r="M82" s="9" t="n">
-        <v>-0.7020999999999999</v>
-      </c>
-      <c r="N82" s="10" t="n">
-        <v>-0.01403</v>
-      </c>
-      <c r="O82" s="9" t="n">
-        <v>1.9987</v>
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="11" t="n"/>
+      <c r="F82" s="11" t="n"/>
+      <c r="G82" s="11" t="n"/>
+      <c r="H82" s="11" t="n"/>
+      <c r="I82" s="11" t="n"/>
+      <c r="J82" s="13" t="n">
+        <v>645.901</v>
+      </c>
+      <c r="K82" s="11" t="n"/>
+      <c r="L82" s="11" t="n"/>
+      <c r="M82" s="11" t="n"/>
+      <c r="N82" s="11" t="n"/>
+      <c r="O82" s="14" t="n">
+        <v>2.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>INE570L01029</t>
+          <t>INE0CZ201020</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>SAI Life Sciences Ltd</t>
+          <t>ANTHEM BIOSCIENCES LIMITED</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4189,52 +4159,52 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F83" s="6" t="n">
-        <v>2757771</v>
+        <v>6335897</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>1221.3</v>
+        <v>761.7</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>336.8066</v>
+        <v>482.6053</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>1221.3</v>
+        <v>761.7</v>
       </c>
       <c r="J83" s="8" t="n">
-        <v>336.8066</v>
+        <v>482.6053</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>1205</v>
+        <v>767.0859</v>
       </c>
       <c r="L83" s="8" t="n">
-        <v>332.3114</v>
+        <v>486.0177</v>
       </c>
       <c r="M83" s="9" t="n">
-        <v>1.3527</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="N83" s="10" t="n">
-        <v>0.01759</v>
+        <v>-0.01308</v>
       </c>
       <c r="O83" s="9" t="n">
-        <v>1.3004</v>
+        <v>1.8633</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>INE044A01036</t>
+          <t>INE570L01029</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>SAI Life Sciences Ltd</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -4248,48 +4218,48 @@
         </is>
       </c>
       <c r="F84" s="6" t="n">
-        <v>1808066</v>
+        <v>3912935</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>1862.8</v>
+        <v>1221.3</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>336.8065</v>
+        <v>477.8868</v>
       </c>
       <c r="I84" s="7" t="n">
-        <v>1862.8</v>
+        <v>1221.3</v>
       </c>
       <c r="J84" s="8" t="n">
-        <v>336.8065</v>
+        <v>477.8868</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>1874.4</v>
+        <v>1205</v>
       </c>
       <c r="L84" s="8" t="n">
-        <v>338.9039</v>
+        <v>471.5087</v>
       </c>
       <c r="M84" s="9" t="n">
-        <v>-0.6189</v>
+        <v>1.3527</v>
       </c>
       <c r="N84" s="10" t="n">
-        <v>-0.00805</v>
+        <v>0.02496</v>
       </c>
       <c r="O84" s="9" t="n">
-        <v>1.3004</v>
+        <v>1.8451</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>INE634S01028</t>
+          <t>INE044A01036</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Mankind Pharma Ltd</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -4299,52 +4269,52 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1066926</v>
+        <v>1841317</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>2462.3</v>
+        <v>1862.8</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>262.7092</v>
+        <v>343.0005</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>2462.3</v>
+        <v>1862.8</v>
       </c>
       <c r="J85" s="8" t="n">
-        <v>262.7092</v>
+        <v>343.0005</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>2483</v>
+        <v>1874.4</v>
       </c>
       <c r="L85" s="8" t="n">
-        <v>264.9177</v>
+        <v>345.1365</v>
       </c>
       <c r="M85" s="9" t="n">
-        <v>-0.8337</v>
+        <v>-0.6189</v>
       </c>
       <c r="N85" s="10" t="n">
-        <v>-0.008460000000000001</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="O85" s="9" t="n">
-        <v>1.0143</v>
+        <v>1.3243</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>INE624Z01016</t>
+          <t>INE634S01028</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Limited</t>
+          <t>Mankind Pharma Ltd</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -4354,43 +4324,43 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F86" s="6" t="n">
-        <v>4019414</v>
+        <v>1361420</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>568.05</v>
+        <v>2462.3</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>228.3228</v>
+        <v>335.2224</v>
       </c>
       <c r="I86" s="7" t="n">
-        <v>568.05</v>
+        <v>2462.3</v>
       </c>
       <c r="J86" s="8" t="n">
-        <v>228.3228</v>
+        <v>335.2224</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>572.3</v>
+        <v>2483</v>
       </c>
       <c r="L86" s="8" t="n">
-        <v>230.0311</v>
+        <v>338.0406</v>
       </c>
       <c r="M86" s="9" t="n">
-        <v>-0.7426</v>
+        <v>-0.8337</v>
       </c>
       <c r="N86" s="10" t="n">
-        <v>-0.00655</v>
+        <v>-0.01079</v>
       </c>
       <c r="O86" s="9" t="n">
-        <v>0.8816000000000001</v>
+        <v>1.2943</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
@@ -4413,208 +4383,208 @@
         </is>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1342031</v>
+        <v>2126615</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>1556</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>208.82</v>
+        <v>330.9013</v>
       </c>
       <c r="I87" s="7" t="n">
         <v>1556</v>
       </c>
       <c r="J87" s="8" t="n">
-        <v>208.82</v>
+        <v>330.9013</v>
       </c>
       <c r="K87" s="7" t="n">
         <v>1564</v>
       </c>
       <c r="L87" s="8" t="n">
-        <v>209.8936</v>
+        <v>332.6026</v>
       </c>
       <c r="M87" s="9" t="n">
         <v>-0.5115</v>
       </c>
       <c r="N87" s="10" t="n">
-        <v>-0.00412</v>
+        <v>-0.00653</v>
       </c>
       <c r="O87" s="9" t="n">
-        <v>0.8063</v>
+        <v>1.2776</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="11" t="n"/>
-      <c r="B88" s="11" t="n"/>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="A88" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>INE624Z01016</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Limited</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>4019414</v>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>568.05</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>228.3228</v>
+      </c>
+      <c r="I88" s="7" t="n">
+        <v>568.05</v>
+      </c>
+      <c r="J88" s="8" t="n">
+        <v>228.3228</v>
+      </c>
+      <c r="K88" s="7" t="n">
+        <v>572.3</v>
+      </c>
+      <c r="L88" s="8" t="n">
+        <v>230.0311</v>
+      </c>
+      <c r="M88" s="9" t="n">
+        <v>-0.7426</v>
+      </c>
+      <c r="N88" s="10" t="n">
+        <v>-0.00655</v>
+      </c>
+      <c r="O88" s="9" t="n">
+        <v>0.8816000000000001</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="n"/>
+      <c r="B89" s="11" t="n"/>
+      <c r="C89" s="12" t="inlineStr">
         <is>
           <t>Pharmaceuticals &amp; Biotechnology — subtotal</t>
         </is>
       </c>
-      <c r="D88" s="11" t="n"/>
-      <c r="E88" s="11" t="n"/>
-      <c r="F88" s="11" t="n"/>
-      <c r="G88" s="11" t="n"/>
-      <c r="H88" s="11" t="n"/>
-      <c r="I88" s="11" t="n"/>
-      <c r="J88" s="13" t="n">
-        <v>1891.131</v>
-      </c>
-      <c r="K88" s="11" t="n"/>
-      <c r="L88" s="11" t="n"/>
-      <c r="M88" s="11" t="n"/>
-      <c r="N88" s="11" t="n"/>
-      <c r="O88" s="14" t="n">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="D89" s="11" t="n"/>
+      <c r="E89" s="11" t="n"/>
+      <c r="F89" s="11" t="n"/>
+      <c r="G89" s="11" t="n"/>
+      <c r="H89" s="11" t="n"/>
+      <c r="I89" s="11" t="n"/>
+      <c r="J89" s="13" t="n">
+        <v>2197.939</v>
+      </c>
+      <c r="K89" s="11" t="n"/>
+      <c r="L89" s="11" t="n"/>
+      <c r="M89" s="11" t="n"/>
+      <c r="N89" s="11" t="n"/>
+      <c r="O89" s="14" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>INE671H01015</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>Sobha Limited</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>Realty</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F89" s="6" t="n">
+      <c r="F90" s="6" t="n">
         <v>1615567</v>
       </c>
-      <c r="G89" s="7" t="n">
+      <c r="G90" s="7" t="n">
         <v>1408</v>
       </c>
-      <c r="H89" s="8" t="n">
+      <c r="H90" s="8" t="n">
         <v>227.4718</v>
       </c>
-      <c r="I89" s="7" t="n">
+      <c r="I90" s="7" t="n">
         <v>1408</v>
       </c>
-      <c r="J89" s="8" t="n">
+      <c r="J90" s="8" t="n">
         <v>227.4718</v>
       </c>
-      <c r="K89" s="7" t="n">
+      <c r="K90" s="7" t="n">
         <v>1428.1</v>
       </c>
-      <c r="L89" s="8" t="n">
+      <c r="L90" s="8" t="n">
         <v>230.7191</v>
       </c>
-      <c r="M89" s="9" t="n">
+      <c r="M90" s="9" t="n">
         <v>-1.4075</v>
       </c>
-      <c r="N89" s="10" t="n">
+      <c r="N90" s="10" t="n">
         <v>-0.01236</v>
       </c>
-      <c r="O89" s="9" t="n">
+      <c r="O90" s="9" t="n">
         <v>0.8783</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="11" t="n"/>
-      <c r="B90" s="11" t="n"/>
-      <c r="C90" s="12" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="11" t="n"/>
+      <c r="B91" s="11" t="n"/>
+      <c r="C91" s="12" t="inlineStr">
         <is>
           <t>Realty — subtotal</t>
         </is>
       </c>
-      <c r="D90" s="11" t="n"/>
-      <c r="E90" s="11" t="n"/>
-      <c r="F90" s="11" t="n"/>
-      <c r="G90" s="11" t="n"/>
-      <c r="H90" s="11" t="n"/>
-      <c r="I90" s="11" t="n"/>
-      <c r="J90" s="13" t="n">
+      <c r="D91" s="11" t="n"/>
+      <c r="E91" s="11" t="n"/>
+      <c r="F91" s="11" t="n"/>
+      <c r="G91" s="11" t="n"/>
+      <c r="H91" s="11" t="n"/>
+      <c r="I91" s="11" t="n"/>
+      <c r="J91" s="13" t="n">
         <v>227.472</v>
       </c>
-      <c r="K90" s="11" t="n"/>
-      <c r="L90" s="11" t="n"/>
-      <c r="M90" s="11" t="n"/>
-      <c r="N90" s="11" t="n"/>
-      <c r="O90" s="14" t="n">
+      <c r="K91" s="11" t="n"/>
+      <c r="L91" s="11" t="n"/>
+      <c r="M91" s="11" t="n"/>
+      <c r="N91" s="11" t="n"/>
+      <c r="O91" s="14" t="n">
         <v>0.88</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>INE956O01016</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>Lenskart Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>Retailing</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>tactical</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="n">
-        <v>12971916</v>
-      </c>
-      <c r="G91" s="7" t="n">
-        <v>508.9</v>
-      </c>
-      <c r="H91" s="8" t="n">
-        <v>660.1408</v>
-      </c>
-      <c r="I91" s="7" t="n">
-        <v>508.9</v>
-      </c>
-      <c r="J91" s="8" t="n">
-        <v>660.1408</v>
-      </c>
-      <c r="K91" s="7" t="n">
-        <v>516.35</v>
-      </c>
-      <c r="L91" s="8" t="n">
-        <v>669.8049</v>
-      </c>
-      <c r="M91" s="9" t="n">
-        <v>-1.4428</v>
-      </c>
-      <c r="N91" s="10" t="n">
-        <v>-0.03677</v>
-      </c>
-      <c r="O91" s="9" t="n">
-        <v>2.5488</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>INE192R01011</t>
+          <t>INE956O01016</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Limited</t>
+          <t>Lenskart Solutions Ltd</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4624,52 +4594,52 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F92" s="6" t="n">
-        <v>1019533</v>
+        <v>10632408</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>4294.6</v>
+        <v>508.9</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>437.8486</v>
+        <v>541.0832</v>
       </c>
       <c r="I92" s="7" t="n">
-        <v>4294.6</v>
+        <v>508.9</v>
       </c>
       <c r="J92" s="8" t="n">
-        <v>437.8486</v>
+        <v>541.0832</v>
       </c>
       <c r="K92" s="7" t="n">
-        <v>4336</v>
+        <v>516.35</v>
       </c>
       <c r="L92" s="8" t="n">
-        <v>442.0695</v>
+        <v>549.0044</v>
       </c>
       <c r="M92" s="9" t="n">
-        <v>-0.9548</v>
+        <v>-1.4428</v>
       </c>
       <c r="N92" s="10" t="n">
-        <v>-0.01614</v>
+        <v>-0.03014</v>
       </c>
       <c r="O92" s="9" t="n">
-        <v>1.6905</v>
+        <v>2.0891</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>INE849A01020</t>
+          <t>INE0VDM01015</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Trent Limited</t>
+          <t>MEESHO LTD</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -4683,48 +4653,48 @@
         </is>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1340440</v>
+        <v>25660887</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>3216.2</v>
+        <v>186.45</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>431.1123</v>
+        <v>478.4472</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>3216.2</v>
+        <v>186.45</v>
       </c>
       <c r="J93" s="8" t="n">
-        <v>431.1123</v>
+        <v>478.4472</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>3247</v>
+        <v>188.37</v>
       </c>
       <c r="L93" s="8" t="n">
-        <v>435.2409</v>
+        <v>483.3741</v>
       </c>
       <c r="M93" s="9" t="n">
-        <v>-0.9486</v>
+        <v>-1.0193</v>
       </c>
       <c r="N93" s="10" t="n">
-        <v>-0.01579</v>
+        <v>-0.01883</v>
       </c>
       <c r="O93" s="9" t="n">
-        <v>1.6645</v>
+        <v>1.8473</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>INE758T01015</t>
+          <t>INE192R01011</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Eternal Limited</t>
+          <t>Avenue Supermarts Limited</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -4738,48 +4708,48 @@
         </is>
       </c>
       <c r="F94" s="6" t="n">
-        <v>15576395</v>
+        <v>839434</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>255.15</v>
+        <v>4294.6</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>397.4317</v>
+        <v>360.5033</v>
       </c>
       <c r="I94" s="7" t="n">
-        <v>255.15</v>
+        <v>4294.6</v>
       </c>
       <c r="J94" s="8" t="n">
-        <v>397.4317</v>
+        <v>360.5033</v>
       </c>
       <c r="K94" s="7" t="n">
-        <v>256.35</v>
+        <v>4336</v>
       </c>
       <c r="L94" s="8" t="n">
-        <v>399.3009</v>
+        <v>363.9786</v>
       </c>
       <c r="M94" s="9" t="n">
-        <v>-0.4681</v>
+        <v>-0.9548</v>
       </c>
       <c r="N94" s="10" t="n">
-        <v>-0.00718</v>
+        <v>-0.01329</v>
       </c>
       <c r="O94" s="9" t="n">
-        <v>1.5345</v>
+        <v>1.3919</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>INE0VDM01015</t>
+          <t>INE849A01020</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>MEESHO LTD</t>
+          <t>Trent Limited</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -4793,254 +4763,254 @@
         </is>
       </c>
       <c r="F95" s="6" t="n">
-        <v>18786742</v>
+        <v>1073210</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>186.45</v>
+        <v>3216.2</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>350.2788</v>
+        <v>345.1658</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>186.45</v>
+        <v>3216.2</v>
       </c>
       <c r="J95" s="8" t="n">
-        <v>350.2788</v>
+        <v>345.1658</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>188.37</v>
+        <v>3247</v>
       </c>
       <c r="L95" s="8" t="n">
-        <v>353.8859</v>
+        <v>348.4713</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>-1.0193</v>
+        <v>-0.9486</v>
       </c>
       <c r="N95" s="10" t="n">
-        <v>-0.01379</v>
+        <v>-0.01264</v>
       </c>
       <c r="O95" s="9" t="n">
-        <v>1.3524</v>
+        <v>1.3327</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>INE758T01015</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Eternal Limited</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Retailing</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>9382218</v>
+      </c>
+      <c r="G96" s="7" t="n">
+        <v>255.15</v>
+      </c>
+      <c r="H96" s="8" t="n">
+        <v>239.3873</v>
+      </c>
+      <c r="I96" s="7" t="n">
+        <v>255.15</v>
+      </c>
+      <c r="J96" s="8" t="n">
+        <v>239.3873</v>
+      </c>
+      <c r="K96" s="7" t="n">
+        <v>256.35</v>
+      </c>
+      <c r="L96" s="8" t="n">
+        <v>240.5132</v>
+      </c>
+      <c r="M96" s="9" t="n">
+        <v>-0.4681</v>
+      </c>
+      <c r="N96" s="10" t="n">
+        <v>-0.00433</v>
+      </c>
+      <c r="O96" s="9" t="n">
+        <v>0.9243</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>INE825V01034</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>Vedant Fashions Private Limited</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>Retailing</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F96" s="6" t="n">
+      <c r="F97" s="6" t="n">
         <v>3098328</v>
       </c>
-      <c r="G96" s="7" t="n">
+      <c r="G97" s="7" t="n">
         <v>412.6</v>
       </c>
-      <c r="H96" s="8" t="n">
+      <c r="H97" s="8" t="n">
         <v>127.837</v>
       </c>
-      <c r="I96" s="7" t="n">
+      <c r="I97" s="7" t="n">
         <v>412.6</v>
       </c>
-      <c r="J96" s="8" t="n">
+      <c r="J97" s="8" t="n">
         <v>127.837</v>
       </c>
-      <c r="K96" s="7" t="n">
+      <c r="K97" s="7" t="n">
         <v>411.4</v>
       </c>
-      <c r="L96" s="8" t="n">
+      <c r="L97" s="8" t="n">
         <v>127.4652</v>
       </c>
-      <c r="M96" s="9" t="n">
+      <c r="M97" s="9" t="n">
         <v>0.2917</v>
       </c>
-      <c r="N96" s="10" t="n">
+      <c r="N97" s="10" t="n">
         <v>0.00144</v>
       </c>
-      <c r="O96" s="9" t="n">
+      <c r="O97" s="9" t="n">
         <v>0.4936</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="11" t="n"/>
-      <c r="B97" s="11" t="n"/>
-      <c r="C97" s="12" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="11" t="n"/>
+      <c r="B98" s="11" t="n"/>
+      <c r="C98" s="12" t="inlineStr">
         <is>
           <t>Retailing — subtotal</t>
         </is>
       </c>
-      <c r="D97" s="11" t="n"/>
-      <c r="E97" s="11" t="n"/>
-      <c r="F97" s="11" t="n"/>
-      <c r="G97" s="11" t="n"/>
-      <c r="H97" s="11" t="n"/>
-      <c r="I97" s="11" t="n"/>
-      <c r="J97" s="13" t="n">
-        <v>2404.649</v>
-      </c>
-      <c r="K97" s="11" t="n"/>
-      <c r="L97" s="11" t="n"/>
-      <c r="M97" s="11" t="n"/>
-      <c r="N97" s="11" t="n"/>
-      <c r="O97" s="14" t="n">
-        <v>9.279999999999999</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="D98" s="11" t="n"/>
+      <c r="E98" s="11" t="n"/>
+      <c r="F98" s="11" t="n"/>
+      <c r="G98" s="11" t="n"/>
+      <c r="H98" s="11" t="n"/>
+      <c r="I98" s="11" t="n"/>
+      <c r="J98" s="13" t="n">
+        <v>2092.424</v>
+      </c>
+      <c r="K98" s="11" t="n"/>
+      <c r="L98" s="11" t="n"/>
+      <c r="M98" s="11" t="n"/>
+      <c r="N98" s="11" t="n"/>
+      <c r="O98" s="14" t="n">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>INE397D01024</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>Bharti Airtel Limited</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>Telecom - Services</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F98" s="6" t="n">
-        <v>2183865</v>
-      </c>
-      <c r="G98" s="7" t="n">
+      <c r="F99" s="6" t="n">
+        <v>1493351</v>
+      </c>
+      <c r="G99" s="7" t="n">
         <v>1850.7</v>
       </c>
-      <c r="H98" s="8" t="n">
-        <v>404.1679</v>
-      </c>
-      <c r="I98" s="7" t="n">
+      <c r="H99" s="8" t="n">
+        <v>276.3745</v>
+      </c>
+      <c r="I99" s="7" t="n">
         <v>1850.7</v>
       </c>
-      <c r="J98" s="8" t="n">
-        <v>404.1679</v>
-      </c>
-      <c r="K98" s="7" t="n">
+      <c r="J99" s="8" t="n">
+        <v>276.3745</v>
+      </c>
+      <c r="K99" s="7" t="n">
         <v>1877.3</v>
       </c>
-      <c r="L98" s="8" t="n">
-        <v>409.977</v>
-      </c>
-      <c r="M98" s="9" t="n">
+      <c r="L99" s="8" t="n">
+        <v>280.3468</v>
+      </c>
+      <c r="M99" s="9" t="n">
         <v>-1.4169</v>
       </c>
-      <c r="N98" s="10" t="n">
-        <v>-0.02211</v>
-      </c>
-      <c r="O98" s="9" t="n">
-        <v>1.5605</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="11" t="n"/>
-      <c r="B99" s="11" t="n"/>
-      <c r="C99" s="12" t="inlineStr">
+      <c r="N99" s="10" t="n">
+        <v>-0.01512</v>
+      </c>
+      <c r="O99" s="9" t="n">
+        <v>1.0671</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="n"/>
+      <c r="B100" s="11" t="n"/>
+      <c r="C100" s="12" t="inlineStr">
         <is>
           <t>Telecom - Services — subtotal</t>
         </is>
       </c>
-      <c r="D99" s="11" t="n"/>
-      <c r="E99" s="11" t="n"/>
-      <c r="F99" s="11" t="n"/>
-      <c r="G99" s="11" t="n"/>
-      <c r="H99" s="11" t="n"/>
-      <c r="I99" s="11" t="n"/>
-      <c r="J99" s="13" t="n">
-        <v>404.168</v>
-      </c>
-      <c r="K99" s="11" t="n"/>
-      <c r="L99" s="11" t="n"/>
-      <c r="M99" s="11" t="n"/>
-      <c r="N99" s="11" t="n"/>
-      <c r="O99" s="14" t="n">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>INE776C01039</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>GMR Airport Ltd</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>Transport Infrastructure</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>cyclical</t>
-        </is>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>22983847</v>
-      </c>
-      <c r="G100" s="7" t="n">
-        <v>108.44</v>
-      </c>
-      <c r="H100" s="8" t="n">
-        <v>249.2368</v>
-      </c>
-      <c r="I100" s="7" t="n">
-        <v>108.44</v>
-      </c>
-      <c r="J100" s="8" t="n">
-        <v>249.2368</v>
-      </c>
-      <c r="K100" s="7" t="n">
-        <v>108.07</v>
-      </c>
-      <c r="L100" s="8" t="n">
-        <v>248.3864</v>
-      </c>
-      <c r="M100" s="9" t="n">
-        <v>0.3424</v>
-      </c>
-      <c r="N100" s="10" t="n">
-        <v>0.00329</v>
-      </c>
-      <c r="O100" s="9" t="n">
-        <v>0.9623</v>
+      <c r="D100" s="11" t="n"/>
+      <c r="E100" s="11" t="n"/>
+      <c r="F100" s="11" t="n"/>
+      <c r="G100" s="11" t="n"/>
+      <c r="H100" s="11" t="n"/>
+      <c r="I100" s="11" t="n"/>
+      <c r="J100" s="13" t="n">
+        <v>276.375</v>
+      </c>
+      <c r="K100" s="11" t="n"/>
+      <c r="L100" s="11" t="n"/>
+      <c r="M100" s="11" t="n"/>
+      <c r="N100" s="11" t="n"/>
+      <c r="O100" s="14" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
@@ -5063,131 +5033,186 @@
         </is>
       </c>
       <c r="F101" s="6" t="n">
-        <v>562594</v>
+        <v>1884491</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>1796</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>101.0419</v>
+        <v>338.4546</v>
       </c>
       <c r="I101" s="7" t="n">
         <v>1796</v>
       </c>
       <c r="J101" s="8" t="n">
-        <v>101.0419</v>
+        <v>338.4546</v>
       </c>
       <c r="K101" s="7" t="n">
         <v>1813.3</v>
       </c>
       <c r="L101" s="8" t="n">
-        <v>102.0152</v>
+        <v>341.7148</v>
       </c>
       <c r="M101" s="9" t="n">
         <v>-0.9540999999999999</v>
       </c>
       <c r="N101" s="10" t="n">
-        <v>-0.00372</v>
+        <v>-0.01247</v>
       </c>
       <c r="O101" s="9" t="n">
-        <v>0.3901</v>
+        <v>1.3068</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="n"/>
-      <c r="B102" s="11" t="n"/>
-      <c r="C102" s="12" t="inlineStr">
+      <c r="A102" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>INE776C01039</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>GMR Airport Ltd</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Transport Infrastructure</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>cyclical</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>20796687</v>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>108.44</v>
+      </c>
+      <c r="H102" s="8" t="n">
+        <v>225.5193</v>
+      </c>
+      <c r="I102" s="7" t="n">
+        <v>108.44</v>
+      </c>
+      <c r="J102" s="8" t="n">
+        <v>225.5193</v>
+      </c>
+      <c r="K102" s="7" t="n">
+        <v>108.07</v>
+      </c>
+      <c r="L102" s="8" t="n">
+        <v>224.7498</v>
+      </c>
+      <c r="M102" s="9" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="N102" s="10" t="n">
+        <v>0.00298</v>
+      </c>
+      <c r="O102" s="9" t="n">
+        <v>0.8707</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="n"/>
+      <c r="B103" s="11" t="n"/>
+      <c r="C103" s="12" t="inlineStr">
         <is>
           <t>Transport Infrastructure — subtotal</t>
         </is>
       </c>
-      <c r="D102" s="11" t="n"/>
-      <c r="E102" s="11" t="n"/>
-      <c r="F102" s="11" t="n"/>
-      <c r="G102" s="11" t="n"/>
-      <c r="H102" s="11" t="n"/>
-      <c r="I102" s="11" t="n"/>
-      <c r="J102" s="13" t="n">
-        <v>350.279</v>
-      </c>
-      <c r="K102" s="11" t="n"/>
-      <c r="L102" s="11" t="n"/>
-      <c r="M102" s="11" t="n"/>
-      <c r="N102" s="11" t="n"/>
-      <c r="O102" s="14" t="n">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="C104" s="15" t="n">
-        <v>24604.905</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>₹cr</t>
-        </is>
+      <c r="D103" s="11" t="n"/>
+      <c r="E103" s="11" t="n"/>
+      <c r="F103" s="11" t="n"/>
+      <c r="G103" s="11" t="n"/>
+      <c r="H103" s="11" t="n"/>
+      <c r="I103" s="11" t="n"/>
+      <c r="J103" s="13" t="n">
+        <v>563.974</v>
+      </c>
+      <c r="K103" s="11" t="n"/>
+      <c r="L103" s="11" t="n"/>
+      <c r="M103" s="11" t="n"/>
+      <c r="N103" s="11" t="n"/>
+      <c r="O103" s="14" t="n">
+        <v>2.18</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>EQUITY</t>
         </is>
       </c>
       <c r="C105" s="15" t="n">
-        <v>1294.995</v>
+        <v>24604.905</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>₹cr (5.0%)</t>
+          <t>₹cr</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>TOTAL (NAV base)</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C106" s="15" t="n">
-        <v>25899.9</v>
+        <v>1294.995</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>₹cr</t>
+          <t>₹cr (5.0%)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>HOLDINGS</t>
+          <t>TOTAL (NAV base)</t>
         </is>
       </c>
       <c r="C107" s="15" t="n">
-        <v>70</v>
+        <v>25899.9</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>names</t>
+          <t>₹cr</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="2" t="inlineStr">
         <is>
+          <t>HOLDINGS</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>names</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>DAY RETURN</t>
         </is>
       </c>
-      <c r="C108" s="15" t="n">
-        <v>-0.1433</v>
-      </c>
-      <c r="D108" t="inlineStr">
+      <c r="C109" s="15" t="n">
+        <v>-0.1654</v>
+      </c>
+      <c r="D109" t="inlineStr">
         <is>
           <t>%</t>
         </is>
